--- a/results/Int Task Remove ACC 0.3/Rando_fi_all.xlsx
+++ b/results/Int Task Remove ACC 0.3/Rando_fi_all.xlsx
@@ -876,7 +876,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.001281024819855936 +/- 0.002241793434747791</t>
+          <t>-0.0014811849479583362 +/- 0.0012148911853877666</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -886,157 +886,157 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-0.0008406725380303848 +/- 0.002578572124129374</t>
+          <t>-0.0031224979983986876 +/- 0.0022982706316104777</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.0006405124099279847 +/- 0.001229967293493794</t>
+          <t>-0.005004003202562035 +/- 0.001532238527542408</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.003642914331465219 +/- 0.0011664373326127659</t>
+          <t>-0.00024019215372295122 +/- 0.001389059373330476</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.00012009607686150892 +/- 0.0013640292263731699</t>
+          <t>0.0012810248198559138 +/- 0.001951330281337706</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.008927141713370723 +/- 0.001953382369696679</t>
+          <t>0.004683746997598093 +/- 0.0014102413894161866</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>0.0 +/- 0.0002531847606219627</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.0035228182546037214 +/- 0.0011151631927288897</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>-0.01589271417133705 +/- 0.0024287928442141625</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-0.017133706965572437 +/- 0.003171385479637847</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>-0.004443554843875075 +/- 0.0018471212161824445</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>-0.0032425940752601745 +/- 0.0009031636647460943</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>4.003202562051778e-05 +/- 0.0016157274676229455</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0.013690952762209784 +/- 0.0028633394303038545</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>-0.006645316253002365 +/- 0.00390676473939338</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0.0034827862289832146 +/- 0.0015612489991993492</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>-0.00048038430744592466 +/- 0.0017246324442384284</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>-0.019255404323458746 +/- 0.0024576533992267057</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0.0016813450760608695 +/- 0.0016965268294969796</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
           <t>4.003202562049557e-05 +/- 0.00012009607686148671</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.0036028823058447124 +/- 0.000996789399358565</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>-0.00356285028022415 +/- 0.002747083821344722</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-0.02049639711769411 +/- 0.002453411280391436</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>0.0015212169735789205 +/- 0.0011574725616333927</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0.003642914331465208 +/- 0.0008669498730066961</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>-0.0038030424339471126 +/- 0.0014125123109989973</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0.012169735788630943 +/- 0.001423249706535739</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>-0.010968775020015952 +/- 0.003785937683758818</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0.00372297838270621 +/- 0.0012791469422474278</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0.0005604483586869935 +/- 0.0016525033979624048</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>-0.003682946357085637 +/- 0.0019513302813377088</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>0.001561248999199416 +/- 0.0015238483835607912</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0.00012009607686148671 +/- 0.00018344978762833248</t>
-        </is>
-      </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.028102481985588422 +/- 0.00281251690476386</t>
+          <t>-0.015972778222578043 +/- 0.0021367503835200033</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.0030824659727782698 +/- 0.0012538398529516014</t>
+          <t>-0.00320256204963969 +/- 0.001074171966773341</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>-0.002041633306645274 +/- 0.0010955910475103062</t>
+          <t>-0.0021216973578862654 +/- 0.0007392388035475984</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.002401921537229834 +/- 0.0009967893993585916</t>
+          <t>-0.00012009607686147561 +/- 0.0013039629683668777</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.0006805444355484025 +/- 0.0013522294438794663</t>
+          <t>0.0011208967173739093 +/- 0.0015992781709718393</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.0011609287429944714 +/- 0.00045467640879106393</t>
+          <t>-0.0004403522818254513 +/- 0.0008482634147484649</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>-0.010568454763811009 +/- 0.002733926513845307</t>
+          <t>-0.00420336269015209 +/- 0.0021798163955263367</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-0.0049639711769415285 +/- 0.0019215372297838249</t>
+          <t>-0.007566052842273819 +/- 0.002129237173254156</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0.006925540432345922 +/- 0.0013039629683668937</t>
+          <t>0.0023618895116093164 +/- 0.0013803794755457824</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00980784627702166 +/- 0.0017654985645476327</t>
+          <t>0.004763811048839095 +/- 0.0012201561772720684</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>-0.0007205764611689202 +/- 0.0001601281024819823</t>
+          <t>-0.000280224179343469 +/- 0.00053857582254097</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.0011609287429944603 +/- 0.0005503493628850282</t>
+          <t>-0.0011609287429943716 +/- 0.00033253097930015626</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -1046,272 +1046,272 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.0075260208166533895 +/- 0.0008164963192302129</t>
+          <t>0.007926341072858323 +/- 0.001349263374407744</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.0027622097678142053 +/- 0.0018384247403050627</t>
+          <t>-0.0010808646917533804 +/- 0.0009481760834529036</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0002531847606219627</t>
+          <t>0.0007606084867894158 +/- 0.00033253097930015626</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-0.001401120896717345 +/- 0.0008996078884805352</t>
+          <t>0.000280224179343469 +/- 0.0005951188449687029</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.0006805444355484913 +/- 0.0016988867232924758</t>
+          <t>-0.005364291433146507 +/- 0.0017375928273987637</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>4.003202562052888e-05 +/- 0.0010039980947946097</t>
+          <t>0.008086469175340305 +/- 0.0011294424323191317</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>0.0006405124099279957 +/- 0.0005126600670483027</t>
+          <t>0.00048038430744595795 +/- 0.0009093528175821094</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.004683746997598048 +/- 0.0006945296866652667</t>
+          <t>0.000600480384307478 +/- 0.0016913234727203947</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.0005204163330664091 +/- 0.001465959441441203</t>
+          <t>-0.0014411529223378404 +/- 0.0010315531406505092</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.0025620496397118276 +/- 0.00040824815961510645</t>
+          <t>-0.0010008006405123893 +/- 0.0005731713796347501</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-0.005284227381905493 +/- 0.0019098255311251564</t>
+          <t>-0.0023618895116092496 +/- 0.0013919406445727458</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>-0.001120896717373876 +/- 0.0008358932353010677</t>
+          <t>0.0012009607686149005 +/- 0.0016602435030686677</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-0.003642914331465119 +/- 0.0008291559318338002</t>
+          <t>0.0019615692554043385 +/- 0.0011664373326127947</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-0.01801441152922335 +/- 0.002250355375909564</t>
+          <t>-0.00984787830264211 +/- 0.0022800689937387078</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>0.0017614091273019162 +/- 0.000543020815302252</t>
+          <t>0.002762209767814294 +/- 0.0008291559318337845</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>-0.004763811048839039 +/- 0.0012841485133983676</t>
+          <t>0.0019215372297838318 +/- 0.001129442432319153</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>-0.0035228182546036433 +/- 0.0017884954286380064</t>
+          <t>0.0068855084067254045 +/- 0.0014741355195774341</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-0.003482786228983148 +/- 0.00149839609865597</t>
+          <t>-0.009047237790232176 +/- 0.0012036266115591008</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-0.015292233787029586 +/- 0.0012115889471915004</t>
+          <t>-0.007686148919135283 +/- 0.0015169972234985176</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-0.0016012810248198228 +/- 0.0005063695212439254</t>
+          <t>0.0008006405124099225 +/- 0.000839718853619015</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>0.0006004803843074891 +/- 0.0008056289750800184</t>
+          <t>-0.0016012810248198228 +/- 0.0007161146445155304</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
+          <t>4.003202562049557e-05 +/- 0.00012009607686148671</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>-0.012770216172938331 +/- 0.001555078030388719</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>0.0005204163330664646 +/- 0.001398831481958056</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>0.004883907125700615 +/- 0.0016583118636675869</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>0.0017213771016813984 +/- 0.0015816450172248526</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>-0.002041633306645274 +/- 0.0012841485133983273</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>-0.0009207365892713981 +/- 0.0011746517815148844</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>-0.0009607686148919048 +/- 0.0015106454975270694</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>0.00024019215372297342 +/- 0.00048038430744594683</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>-0.0009207365892713981 +/- 0.0012665566068499638</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>-0.0013210568454763648 +/- 0.0012791469422474314</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>-0.005484387510007993 +/- 0.0017362088424500593</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>-0.0024819855884707365 +/- 0.0008733956857194391</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>-8.006405124099114e-05 +/- 0.0001601281024819823</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>0.010208166533226603 +/- 0.0015322385275423922</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>-0.004283426741393093 +/- 0.0014327886443693712</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>0.000280224179343469 +/- 0.0008213884919408634</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>0.005484387510008038 +/- 0.0017996610722969665</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>-0.0005204163330664424 +/- 0.000840672538030407</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>0.009927942353883123 +/- 0.0017884954286380074</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>-8.006405124099114e-05 +/- 0.0003489911083699427</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>0.0006805444355484247 +/- 0.0005675519166836483</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>0.000960768614891927 +/- 0.000999999679487352</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
         <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>-0.002241793434747752 +/- 0.0006746316872038578</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>-0.014291433146517162 +/- 0.0012665566068500009</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>-0.005644515612489953 +/- 0.0017763577047505078</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>0.0007606084867894603 +/- 0.0008291559318338195</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>-0.00768614891913526 +/- 0.0004999998397436564</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>-0.009807846277021559 +/- 0.0011216113471675044</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>-0.006765412329863862 +/- 0.0009379803453850873</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>0.0032025620496397567 +/- 0.0013751452391767265</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>-0.00012009607686148671 +/- 0.00031266011512836244</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>0.008206565252201804 +/- 0.0017925230726371377</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>0.009567654123298663 +/- 0.0012461475113108935</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>-0.00028022417934345787 +/- 0.0008213884919408888</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>0.010928742994395547 +/- 0.0017082936984268977</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>0.011609287429943993 +/- 0.0019447490474765682</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>0.018374699759807867 +/- 0.0020369182118828797</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>-0.0003202562049639646 +/- 0.0001601281024819823</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>0.0023218574859888543 +/- 0.0007553227487635235</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>0.0008406725380304958 +/- 0.0002802241793435039</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>-0.0007606084867894158 +/- 0.00045467640879104533</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>0.007325860688550856 +/- 0.001443930247948091</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
         <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>-0.0024419535628502297 +/- 0.0006316947092897988</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>0.003242594075260252 +/- 0.001065934904379029</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.00380304243394719 +/- 0.0011216113471674628</t>
+          <t>0.0022417934347478074 +/- 0.0008987167462227551</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>-0.0031224979983986655 +/- 0.0009607686148919132</t>
+          <t>0.0008406725380304292 +/- 0.001220156177272082</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>0.006845476381104931 +/- 0.0016837262485839253</t>
+          <t>0.006565252201761429 +/- 0.0017920760036508857</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>0.0023618895116093498 +/- 0.0005204163330664424</t>
+          <t>-0.0006805444355484247 +/- 0.0007606084867894158</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>0.007526020816653378 +/- 0.000993568746676611</t>
+          <t>-0.0019215372297837873 +/- 0.0011982889949636074</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>0.013050440352281856 +/- 0.002251779201028855</t>
+          <t>0.00324259407526023 +/- 0.001138627914597926</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>-0.0015212169735788206 +/- 0.0012760110048446113</t>
+          <t>0.0015612489991993716 +/- 0.0008095976147380873</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.003699033207229907 +/- 0.0014657919944651183</t>
+          <t>0.006893652795292105 +/- 0.0016301571609639008</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1331,157 +1331,157 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.02017654476670868 +/- 0.002093299638165407</t>
+          <t>0.03417402269861284 +/- 0.0013820329737514545</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.00521227406473308 +/- 0.000980403849490595</t>
+          <t>0.0012610340479192739 +/- 0.0015271880726847314</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.00281630937368641 +/- 0.00196305917256588</t>
+          <t>-0.0024800336275746294 +/- 0.0016861009768920987</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.005548549810844882 +/- 0.001429171920975203</t>
+          <t>0.01071878940731399 +/- 0.001345759612743335</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.009962168978562414 +/- 0.002348293858505836</t>
+          <t>0.0021437578814627934 +/- 0.0018652129241138126</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.0005464480874317057 +/- 0.000269151922548702</t>
+          <t>-8.40689365279479e-05 +/- 0.0001681378730558958</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-0.0021017234131988304 +/- 0.0017022662237340576</t>
+          <t>0.005548549810844861 +/- 0.0010432680660774362</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.0021437578814627934 +/- 0.002957088244970419</t>
+          <t>-0.00651534258091635 +/- 0.0036705021430376086</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.012400168137873058 +/- 0.0034979648964046125</t>
+          <t>0.002227826817990719 +/- 0.0035171071283327487</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-0.00042034468263979496 +/- 0.001079885042342592</t>
+          <t>0.003614964270701937 +/- 0.001482571844350424</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.005590584279108857 +/- 0.0010807028274218166</t>
+          <t>0.005884825556956685 +/- 0.0009947170715594205</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.0005884825556956685 +/- 0.0017654476670870135</t>
+          <t>0.006221101303068488 +/- 0.0015705373427717224</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.003068516183270287 +/- 0.002665462608236712</t>
+          <t>0.010214375788146268 +/- 0.0016393442622950828</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>0.002606137032366529 +/- 0.003906266550815957</t>
+          <t>0.011265237494745672 +/- 0.003351178045900767</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>-0.0006305170239596536 +/- 0.0010675430936696356</t>
+          <t>-0.0013030685161832922 +/- 0.0005464480874316792</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.003867171080285836 +/- 0.0008976106138740041</t>
+          <t>0.001008827238335408 +/- 0.001066715219878043</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>-0.01223203026481715 +/- 0.001747845555804273</t>
+          <t>-0.005800756620428771 +/- 0.0012298225168833683</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>0.007608238755779739 +/- 0.0012102715467749454</t>
+          <t>0.004119377889869669 +/- 0.0023084540088685783</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>4.203446826397395e-05 +/- 0.00012610340479192182</t>
+          <t>4.203446826397395e-05 +/- 0.0004388527326149611</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.002942412778478365 +/- 0.002151573584206765</t>
+          <t>0.004918032786885207 +/- 0.001550724400647058</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>-0.005464480874316935 +/- 0.0015950959193787462</t>
+          <t>0.012063892391761222 +/- 0.0011129215884719528</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-0.0006305170239596647 +/- 0.0016734787084820822</t>
+          <t>0.0005884825556956242 +/- 0.0011153004759496782</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>-0.0009247583018074934 +/- 0.001326585442459802</t>
+          <t>0.007650273224043691 +/- 0.0008976106138740062</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.0032786885245901566 +/- 0.002014148558337271</t>
+          <t>-0.00567465321563686 +/- 0.0011160923116731196</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.00012610340479194405 +/- 0.0007292707680915454</t>
+          <t>0.0008827238335434751 +/- 0.0007388985217001836</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>-0.006431273644388402 +/- 0.0016176445065064192</t>
+          <t>0.007187894073139955 +/- 0.0023885788390374772</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-0.011937788986969334 +/- 0.002488213297511354</t>
+          <t>-0.0007566204287516087 +/- 0.002923133863087657</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>-0.0074401008827238435 +/- 0.001329911056709246</t>
+          <t>-0.0013871374527112512 +/- 0.0019630591725658775</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>4.203446826396284e-05 +/- 0.0019486047896594043</t>
+          <t>0.010004203446826366 +/- 0.0023007872523588264</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.0002522068095838437 +/- 0.000600372293278098</t>
+          <t>0.00012610340479191073 +/- 0.0006790876175453167</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.0008406893652795566 +/- 0.0006777854349137013</t>
+          <t>-0.00042034468263977274 +/- 0.0006234719198903459</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1491,122 +1491,122 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.011937788986969311 +/- 0.00166235560599287</t>
+          <t>-0.0023959646910466925 +/- 0.001444543108654018</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.008532997057587222 +/- 0.0015620768538093383</t>
+          <t>0.009121479613282867 +/- 0.0027309467626365404</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>0.00130306851618327 +/- 0.00034916451714664257</t>
+          <t>0.0014712063892391547 +/- 0.0010339112127993816</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>0.0002942412778478287 +/- 0.0006525504285943529</t>
+          <t>0.002059688944934823 +/- 0.0010373234703029153</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-0.0026061370323665622 +/- 0.0019335855401429096</t>
+          <t>-0.004833963850357314 +/- 0.0017659480065237473</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>-0.005086170659941158 +/- 0.0015889918597255905</t>
+          <t>0.0003362757461117916 +/- 0.002548550885451731</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-0.0008406893652795566 +/- 0.0008817224448677084</t>
+          <t>-0.0010088272383354745 +/- 0.0004680760288213513</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.008911307271962998 +/- 0.0014291719209752077</t>
+          <t>0.001050861706599382 +/- 0.0008459273559267712</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.004875998318621266 +/- 0.00207805079349446</t>
+          <t>0.00504413619167714 +/- 0.002515052593804385</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>-0.0009247583018075045 +/- 0.0007705045304675644</t>
+          <t>0.0030685161832702534 +/- 0.0009594545784374236</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-0.008617065994115181 +/- 0.0012921753803227926</t>
+          <t>0.010004203446826366 +/- 0.0023007872523588204</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>0.00012610340479191073 +/- 0.001681904079339447</t>
+          <t>0.0034047919293820673 +/- 0.0018557158515883961</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-0.002480033627574618 +/- 0.0014123831539648087</t>
+          <t>0.0033627574611181043 +/- 0.001681378730559055</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-0.0018074821353509906 +/- 0.0006790876175453354</t>
+          <t>0.002269861286254693 +/- 0.0008857212066290676</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>0.0004623791509037356 +/- 0.0006632927212299015</t>
+          <t>0.001008827238335408 +/- 0.0006291143147160947</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>-0.0010508617065994152 +/- 0.0016944635872842635</t>
+          <t>0.0015132408575031287 +/- 0.0010667152198780457</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.005968894493484656 +/- 0.0025623792608874593</t>
+          <t>0.01635140815468682 +/- 0.0016755890229503744</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-0.010718789407314 +/- 0.0017858466402898676</t>
+          <t>-0.015300546448087472 +/- 0.0019463365956772156</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-0.010886927280369907 +/- 0.001836574382089407</t>
+          <t>0.009541824295922619 +/- 0.0021272099081765515</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-0.0010508617065994375 +/- 0.0004699596421815464</t>
+          <t>-0.00021017234131990304 +/- 0.0007807555956707299</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>0.0007566204287515754 +/- 0.0006457457543395247</t>
+          <t>0.0007145859604875682 +/- 0.0005333576099390181</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>-4.203446826397395e-05 +/- 0.00034916451714659845</t>
+          <t>0.0006725514922235831 +/- 0.0003362757461117916</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-0.006683480453972257 +/- 0.0013998172177677082</t>
+          <t>0.0010508617065993708 +/- 0.0018055259852807356</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>0.0016813787305590578 +/- 0.0017331255256904689</t>
+          <t>0.009373686422866734 +/- 0.002007558459228164</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1616,92 +1616,92 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>-4.203446826400725e-05 +/- 0.000738898521700164</t>
+          <t>0.000756620428751531 +/- 0.00036644799861626</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>-0.0015973097940311098 +/- 0.001668720743276941</t>
+          <t>0.0007566204287515532 +/- 0.0014897053507077962</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>-0.0013030685161832922 +/- 0.0011656515026365727</t>
+          <t>0.005044136191677151 +/- 0.002781907037877139</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.00016813787305588467 +/- 0.0005044136191677095</t>
+          <t>0.0002101723413198586 +/- 0.0009991479044980784</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-0.002942412778478354 +/- 0.0012887523931699005</t>
+          <t>-0.007608238755779773 +/- 0.0013084810774504935</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-0.015973097940311064 +/- 0.0016061347771788817</t>
+          <t>-0.01811685582177387 +/- 0.002580587722264952</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-0.00130306851618327 +/- 0.0014615669315438107</t>
+          <t>0.002395964691046637 +/- 0.0009218878604229188</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>0.00021017234131986973 +/- 0.0017858466402898806</t>
+          <t>-0.00029424127784783983 +/- 0.0017336351935520098</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>0.00021017234131986973 +/- 0.0004699596421815166</t>
+          <t>0.0005464480874316612 +/- 0.0003783102143757655</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.008827238335435039 +/- 0.0021017234131988282</t>
+          <t>0.00832282471626732 +/- 0.0010088272383354377</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.00012610340479191073 +/- 0.0016066847291817123</t>
+          <t>-0.000294241277847862 +/- 0.001671365729472133</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.0022698612862547263 +/- 0.000998263311226388</t>
+          <t>0.006052963430012592 +/- 0.0017952212277480195</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>-0.00025220680958385475 +/- 0.0028583438419504</t>
+          <t>0.013829340058848227 +/- 0.0024106685092794827</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>-0.0017654476670870168 +/- 0.0014536878071282346</t>
+          <t>0.004623791509037389 +/- 0.0011588103196376765</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>0.010214375788146258 +/- 0.00273094676263654</t>
+          <t>0.00996216897856238 +/- 0.0023256118022064714</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>-4.203446826397395e-05 +/- 0.00012610340479192182</t>
+          <t>-8.40689365279479e-05 +/- 0.0002522068095838437</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>0.001176965111391337 +/- 0.0005250103403445628</t>
+          <t>0.001092896174863367 +/- 0.0014341086262490113</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>-2.2204460492503132e-17 +/- 0.0009585333544339128</t>
+          <t>0.001050861706599382 +/- 0.0012921753803227635</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1711,52 +1711,52 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>0.0073560319461958845 +/- 0.001795713271399241</t>
+          <t>-0.0002942412778478731 +/- 0.0010131963676497707</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>0.002690205968894499 +/- 0.0010831524780769207</t>
+          <t>0.014081546868432094 +/- 0.0013717670342228462</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>-0.0001681378730559291 +/- 0.0005044136191677317</t>
+          <t>-0.0012189995796553666 +/- 0.000477419785271147</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>-0.0005044136191677429 +/- 0.0007705045304675669</t>
+          <t>-0.0019756200084069197 +/- 0.0011896571414951689</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>-0.008743169398907114 +/- 0.0014042280864640605</t>
+          <t>0.005170239596469062 +/- 0.0018614199096666255</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>-0.0006305170239596757 +/- 0.001641498460678152</t>
+          <t>0.0019335855401428903 +/- 0.0013711228608911318</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>-4.2034468263985046e-05 +/- 0.0011656515026365758</t>
+          <t>0.0035729298024379853 +/- 0.0005717305804428503</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.003404791929382078 +/- 0.0015091486398500168</t>
+          <t>0.008070617906683463 +/- 0.0019427019770140855</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.008911307271962965 +/- 0.001404228086464069</t>
+          <t>0.01336696090794448 +/- 0.0017105498065889712</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>0.0034468263976460854 +/- 0.0014414819839833697</t>
+          <t>0.011349306431273621 +/- 0.0015950959193787432</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.0019287211740041887 +/- 0.0006812610821497741</t>
+          <t>0.003941299790356356 +/- 0.0008834929771784265</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1776,377 +1776,377 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.0002935010482180367 +/- 0.0010941709308762888</t>
+          <t>-4.192872117403379e-05 +/- 0.0007127882599580912</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.0009224318658280883 +/- 0.0007685661542902838</t>
+          <t>0.003102725366876258 +/- 0.0009597922970448275</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.000251572327044014 +/- 0.0003842830771451268</t>
+          <t>0.0010482180293500786 +/- 0.0006825501298155091</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.0009643605870021 +/- 0.0004612159329140417</t>
+          <t>0.0007547169811320531 +/- 0.0007453412509279523</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.003647798742138375 +/- 0.0009195686456797343</t>
+          <t>0.0023480083857441935 +/- 0.0010473791192282347</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.00016771488469600194 +/- 0.00020540794488746006</t>
+          <t>-1.1102230246251566e-17 +/- 0.00018751094150942454</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.0035220125786163516 +/- 0.001013253331119043</t>
+          <t>8.385744234796766e-05 +/- 0.0010236105338141547</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.007379454926624729 +/- 0.002453457247518284</t>
+          <t>0.012117400419287171 +/- 0.003162493077255028</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.01329140461215934 +/- 0.0022738359518584797</t>
+          <t>0.00758909853249472 +/- 0.0018979405111540868</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.0029350104821802892 +/- 0.0009375547075470782</t>
+          <t>0.002054507337526168 +/- 0.0009459550668912734</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.0009643605870020888 +/- 0.0007028534429450656</t>
+          <t>-0.001257861635220159 +/- 0.0012006558543628109</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.0028092243186582768 +/- 0.0007274361246497862</t>
+          <t>0.0036477987421383307 +/- 0.0005640932514496293</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.005366876310272528 +/- 0.0020265066622381003</t>
+          <t>0.010733752620545035 +/- 0.0018863265206208572</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.016603773584905647 +/- 0.00473701777526157</t>
+          <t>0.004486373165618407 +/- 0.005045577640284659</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.0026415094339622635 +/- 0.0005320158297882426</t>
+          <t>0.003354297693920305 +/- 0.0005303610331519264</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.0012997903563941148 +/- 0.0006061564903480495</t>
+          <t>0.0028930817610062554 +/- 0.0009271842510480628</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.0023060796645702265 +/- 0.001064857450666689</t>
+          <t>0.0015513626834381179 +/- 0.001094170930876305</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.00398322851153039 +/- 0.0011289653683720145</t>
+          <t>0.0018448637316561434 +/- 0.0011281865028992648</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>-4.192872117402269e-05 +/- 0.00022579307367441982</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0.0066666666666666315 +/- 0.0015169855358595791</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>-0.003857442348008422 +/- 0.0015777683624508914</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0.0012159329140460807 +/- 0.000982421342881351</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0.0006289308176100183 +/- 0.0007787914306501822</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>-0.0006708595387840965 +/- 0.0010804275661823832</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>-4.1928721174011584e-05 +/- 0.00012578616352203474</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>-0.0010062893081761448 +/- 0.0014057068858901564</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>-0.0030188679245283347 +/- 0.0010574021142908605</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>-0.004570230607966486 +/- 0.0006616240602959928</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>-0.00419287211740047 +/- 0.0013259025828798116</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>8.385744234800097e-05 +/- 0.00016771488469600196</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0.000922431865828044 +/- 0.0002515723270440473</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0.005450733752620551 +/- 0.0013125765905659186</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>-0.0017190775681341641 +/- 0.0009459550668912755</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0.0009224318658281105 +/- 0.0009524374584151449</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0.001132075471698124 +/- 0.00032747378096041775</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>0.0008805031446540879 +/- 0.0008054244323814844</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>-0.00029350104821800337 +/- 0.0001921415385725549</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>-0.003396226415094328 +/- 0.0015169855358595987</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>0.00012578616352200146 +/- 0.0006233152514599075</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>-0.00046121593291404973 +/- 0.0009271842510480659</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>-0.006037735849056614 +/- 0.0007310522337175213</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0.0007966457023060869 +/- 0.0002935010482180462</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0.00016771488469600194 +/- 0.00020540794488746008</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>-0.010440251572327076 +/- 0.0013185899533347024</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>-0.002641509433962297 +/- 0.0009931001494613804</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>-0.0006708595387841188 +/- 0.0002781236721471787</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>-4.4408920985006264e-17 +/- 0.0007016016993996682</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>0.0023480083857442048 +/- 0.001158932910782826</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>-0.005199161425576549 +/- 0.0008633652109842415</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>0.0005450733752620285 +/- 0.0004213784327514003</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>0.0004192872117399826 +/- 0.0010270397244373955</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>-8.385744234804538e-05 +/- 0.0007685661542902875</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>-0.0005450733752620951 +/- 0.0014286561876226999</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-0.004989517819706535 +/- 0.0010001560118974118</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>-0.008553459119496898 +/- 0.0016792439743816218</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>-8.385744234805648e-05 +/- 0.0007685661542903044</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>-0.0036058700209643966 +/- 0.001405706885890165</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>-8.385744234803427e-05 +/- 0.0002515723270440473</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>-0.0014675052410901724 +/- 0.0008643827307374647</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>-0.0019706498951782224 +/- 0.0013265653685162473</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>0.0013417190775680931 +/- 0.0009707200757056778</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>-0.0012997903563941704 +/- 0.0019527263768880656</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>0.0003354297693920039 +/- 0.00016771488469600194</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>8.385744234800097e-05 +/- 0.00016771488469600196</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0.0010482180293500676 +/- 0.000538584175206085</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>-0.006121593291404659 +/- 0.0017206108619440695</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>-0.001761006289308209 +/- 0.001090146750524109</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
         <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>-0.002012578616352212 +/- 0.0008130280683297931</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>-0.0009224318658280995 +/- 0.0007911095288936444</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>-0.001132075471698124 +/- 0.0003274737809604177</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>0.0009643605870021 +/- 0.0003274737809604547</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>0.00037735849056603766 +/- 0.0006616240602959816</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>-0.0018029350104821762 +/- 0.0010779840781704384</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>-0.0005870020964360512 +/- 0.0005369496215876596</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>0.0016352201257861631 +/- 0.0009824213428813496</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-0.0009643605870021 +/- 0.00075121479526913</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>-0.0032285115303983146 +/- 0.0009002478219532086</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>0.0017610062893081869 +/- 0.0010062893081761088</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>0.002348008385744249 +/- 0.0007776619283434523</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>-8.385744234801207e-05 +/- 0.0005236895596141267</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>-0.0010901467505241124 +/- 0.0006275316371947919</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>0.0002515723270440029 +/- 0.00020540794488746006</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>-0.0012578616352201255 +/- 0.0007731274178023364</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>0.001383647798742138 +/- 0.00104485834753686</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>4.1928721174011584e-05 +/- 0.0009459550668912813</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>0.0009643605870021 +/- 0.0010106474459701572</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>0.0002515723270440251 +/- 0.0004275907348924694</t>
-        </is>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>0.002096436058700235 +/- 0.000324778477669385</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>0.000503144654088028 +/- 0.00016771488469604636</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>-0.0022222222222222253 +/- 0.0006509087922960217</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>-0.0006708595387840633 +/- 0.0009779374247119992</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
+      <c r="BI4" t="inlineStr">
         <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>4.1928721174000484e-05 +/- 0.00012578616352200146</t>
-        </is>
-      </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>-0.0019706498951782003 +/- 0.0006773792210232154</t>
+          <t>-0.0017190775681342086 +/- 0.0003482861158456349</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>0.0022222222222222365 +/- 0.0011258466735511582</t>
+          <t>-0.011572327044025199 +/- 0.001525652444332091</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.0002515723270440029 +/- 0.00020540794488746006</t>
+          <t>-0.00029350104821807 +/- 0.00026847481079385495</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-0.0016771488469601637 +/- 0.0007955415497278881</t>
+          <t>0.0003354297693920039 +/- 0.0007911095288936479</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-0.0016771488469601748 +/- 0.001140584529034428</t>
+          <t>-0.006037735849056624 +/- 0.0018295533944881787</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>0.00037735849056603766 +/- 0.0006061564903480588</t>
+          <t>0.00041928721174001594 +/- 0.0007731274178023424</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>0.0004192872117400381 +/- 0.0005303610331519264</t>
+          <t>-4.192872117404489e-05 +/- 0.0006876821579394758</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>-4.1928721174011584e-05 +/- 0.00034828611584561615</t>
+          <t>-4.1928721174011584e-05 +/- 0.00012578616352203477</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.0007127882599580748 +/- 0.0005944422171386858</t>
+          <t>-4.192872117403379e-05 +/- 0.0007605181193801867</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>-1.1102230246251566e-17 +/- 0.00041928721174002705</t>
+          <t>-0.0020125786163522454 +/- 0.0010901467505241192</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.00033542976939202605 +/- 0.0003137658185974033</t>
+          <t>0.0005450733752620285 +/- 0.000727436124649785</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.0005031446540880502 +/- 0.0005562473442944261</t>
+          <t>0.0020125786163521786 +/- 0.0006441212367185338</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>0.0017610062893081758 +/- 0.00045158614734880874</t>
+          <t>-0.0002935010482180589 +/- 0.00032747378096046746</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>0.0010901467505241014 +/- 0.0009031722946975937</t>
+          <t>0.0007127882599580415 +/- 0.0008805031446540942</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>-4.1928721174000484e-05 +/- 0.00012578616352200143</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>0.0006289308176100738 +/- 0.0005702922645172079</t>
+          <t>-0.0002935010482180811 +/- 0.00019214153857260579</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>0.0014255765199161496 +/- 0.0005369496215876751</t>
+          <t>-0.00029350104821807 +/- 0.00026847481079385495</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2156,12 +2156,12 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>8.385744234800097e-05 +/- 0.00031376581859736776</t>
+          <t>-0.00012578616352203474 +/- 0.00042137843275140804</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>0.0007547169811320864 +/- 0.0008754974011665076</t>
+          <t>4.192872117395607e-05 +/- 0.0007370396574946376</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2171,37 +2171,37 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.00041928721174002705 +/- 0.0002651805165759764</t>
+          <t>0.00041928721174000483 +/- 0.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.001048218029350101 +/- 0.0007322536350764341</t>
+          <t>0.0002935010482179812 +/- 0.0004213784327514003</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0.0024737945492662393 +/- 0.0005118052669070819</t>
+          <t>-0.00025157232704405843 +/- 0.0006275316371947875</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>0.000251572327044014 +/- 0.0002781236721472022</t>
+          <t>-0.00020964360587005793 +/- 0.0002096436058700579</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>0.00012578616352200146 +/- 0.0004978759784921586</t>
+          <t>0.00020964360586998022 +/- 0.0005048886615845749</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>0.0012159329140461138 +/- 0.0008479559084342549</t>
+          <t>0.00016771488469599082 +/- 0.0010304575033496272</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>0.0002935010482180256 +/- 0.0003773584905660364</t>
+          <t>0.0012997903563941148 +/- 0.00100015601189742</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.0022348638764729477 +/- 0.0023360068836740877</t>
+          <t>-0.0062169849654612145 +/- 0.0020882023823697</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2221,157 +2221,157 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.03161316537992689 +/- 0.0026818366517675765</t>
+          <t>-0.026574563185696898 +/- 0.0028915801502896726</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.00040633888663140774 +/- 0.002403933272287539</t>
+          <t>-0.009630231613165407 +/- 0.0020563317235075093</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.0019097927671678284 +/- 0.0022845498247656337</t>
+          <t>0.000853311661926015 +/- 0.00242070231753051</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.01015847216578628 +/- 0.0015526187057734915</t>
+          <t>-0.019504266558309648 +/- 0.002291405474176632</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.009670865501828496 +/- 0.0025557391618880924</t>
+          <t>0.011986997155627777 +/- 0.0028283638448264523</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.0002031694433157427 +/- 0.0008376890746886933</t>
+          <t>0.000406338886631441 +/- 0.00025699127673045954</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.01690369768386831 +/- 0.0011377488825680673</t>
+          <t>0.004347826086956497 +/- 0.0013964112375001723</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.06407964242177973 +/- 0.0035145377596373316</t>
+          <t>0.055221454693214135 +/- 0.004048938140108907</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.05574969524583501 +/- 0.0044800589849127315</t>
+          <t>0.05713124746038193 +/- 0.0035479691105961956</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-0.004307192198293408 +/- 0.0018902402843743113</t>
+          <t>-0.004185290532303943 +/- 0.003561207413995194</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>-0.022551808208045542 +/- 0.0012622693674936192</t>
+          <t>-0.009508329947175964 +/- 0.0023846242586137707</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.0008939455505891702 +/- 0.002600568874441306</t>
+          <t>0.008614384396586728 +/- 0.0023539615372548243</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.011174319382364873 +/- 0.0032823028080868595</t>
+          <t>0.016619260463226305 +/- 0.0035304746623723506</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.012880942706216947 +/- 0.003163446749151073</t>
+          <t>-0.0055668427468508865 +/- 0.0031477497613757416</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.014221861032100746 +/- 0.0024039332722875107</t>
+          <t>0.011011783827712262 +/- 0.002434305696993114</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-0.002844372206420198 +/- 0.0014763024887919553</t>
+          <t>-0.014872003250711118 +/- 0.0016575439296522697</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>-0.006704591629418976 +/- 0.0023075612945145344</t>
+          <t>-0.004997968305566858 +/- 0.0018085504335041153</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.00637952052011378 +/- 0.001762311941666114</t>
+          <t>-0.0035351483136936367 +/- 0.001246473925248099</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.00016253555465257642 +/- 0.00037241574115853165</t>
+          <t>0.00158472165786262 +/- 0.0008217695414935477</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.009711499390491651 +/- 0.003123527840874049</t>
+          <t>0.01901665989435186 +/- 0.003162141642965256</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>-0.003941487200325111 +/- 0.0018976504557229692</t>
+          <t>-0.0015440877691995313 +/- 0.0015925166958362933</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.009305160503860188 +/- 0.0015252600064301922</t>
+          <t>0.007070296627387229 +/- 0.001754330202756837</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.0012596505485574672 +/- 0.0016699490116240982</t>
+          <t>0.004957334416903691 +/- 0.0016028511112000032</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.011418122714343736 +/- 0.0019270062090823957</t>
+          <t>0.009955302722470537 +/- 0.0013629020586142487</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.0006907761072734497 +/- 0.0008533116619260262</t>
+          <t>0.001178382771231179 +/- 0.0008799840645147176</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>-0.01950426655830968 +/- 0.003255786367169458</t>
+          <t>-0.021332791548151188 +/- 0.0023710840245258313</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-0.007720438845997579 +/- 0.001844259360895592</t>
+          <t>-0.006501422186103223 +/- 0.0012849563836523467</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-0.006663957740755832 +/- 0.0014673279224110367</t>
+          <t>-0.0026412027631044555 +/- 0.001638004418589698</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-0.0001219016659894323 +/- 0.0005760847979990853</t>
+          <t>-4.0633888663166304e-05 +/- 0.0010971149939049268</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.0006907761072734497 +/- 0.001060381011840681</t>
+          <t>0.0012596505485574672 +/- 0.0005586236117377975</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.001178382771231179 +/- 0.0006907761072734497</t>
+          <t>-0.0002438033319788646 +/- 0.00045247983444371317</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -2381,122 +2381,122 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.0032507110930515616 +/- 0.0016654938262429294</t>
+          <t>-0.00044697277529460734 +/- 0.00222894565654653</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.0005282405526209177 +/- 0.0018267181465249137</t>
+          <t>0.0012596505485574783 +/- 0.002648693781021081</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.0013815522145468994 +/- 0.000816731054134145</t>
+          <t>0.001625355546525764 +/- 0.0009265952255986273</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.0003657049979682858 +/- 0.000821769541493569</t>
+          <t>0.0009345794392523254 +/- 0.0013725595899272205</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.0092238927265339 +/- 0.0016856943122870035</t>
+          <t>-0.00028443722064205315 +/- 0.002677215182450898</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>-0.0028443722064201648 +/- 0.0018884924890080845</t>
+          <t>-0.005444941080861476 +/- 0.0018190190398699286</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.0019097927671677729 +/- 0.000945120142187138</t>
+          <t>-0.0015847216578626865 +/- 0.0008610166639747135</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.004429093864282774 +/- 0.0024138718797690516</t>
+          <t>0.007192198293376639 +/- 0.0014768615884100979</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.0049167005282405585 +/- 0.0008799840645147377</t>
+          <t>-1.1102230246251566e-17 +/- 0.0011635774939679972</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.0020723283218203603 +/- 0.0011839741799539497</t>
+          <t>-0.007354733848029271 +/- 0.0018748918317853648</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.009630231613165363 +/- 0.0020075772981772914</t>
+          <t>0.023567655424624114 +/- 0.0019739874524975307</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>-0.0034132466477042045 +/- 0.0014896629646341459</t>
+          <t>-0.0015034538805363984 +/- 0.0027622079478841475</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.015440877691995092 +/- 0.0019145418918146866</t>
+          <t>0.008533116619260438 +/- 0.0014874445524358595</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.013815522145469305 +/- 0.0019656053023076395</t>
+          <t>0.020682649329540802 +/- 0.0028353604265614852</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.002275497765136092 +/- 0.0009819622896054183</t>
+          <t>0.00032507110930515284 +/- 0.0006242296422485514</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.02149532710280373 +/- 0.002434305696993106</t>
+          <t>0.004754164973587949 +/- 0.0014198622681557173</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.015765948801300268 +/- 0.0017411040459673738</t>
+          <t>0.008980089394555024 +/- 0.0022437119369814666</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.010036570499796805 +/- 0.0024383719120158387</t>
+          <t>0.0017066233238520634 +/- 0.0020543233904533765</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-0.012880942706217003 +/- 0.0020960943318210387</t>
+          <t>-0.0092645266151971 +/- 0.0016930245149126316</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>0.0012596505485574783 +/- 0.001316061336099273</t>
+          <t>0.001178382771231179 +/- 0.0007370319848523619</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.0001625355546525542 +/- 0.0009301522261080644</t>
+          <t>0.000812677773262882 +/- 0.000812677773262882</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>-0.00032507110930515284 +/- 0.0003981291739590606</t>
+          <t>0.0002031694433157205 +/- 0.00032760088371793417</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-0.013246647704185321 +/- 0.0013378364594192772</t>
+          <t>-0.007436001625355559 +/- 0.0021734382966788154</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.027752945956928055 +/- 0.0015100287831013505</t>
+          <t>0.020601381552214526 +/- 0.0014198622681557244</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2506,92 +2506,92 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>-0.00048760666395777366 +/- 0.0011888450904776972</t>
+          <t>0.0001219016659894323 +/- 0.0005155862470722967</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0.01901665989435185 +/- 0.0024298929520887406</t>
+          <t>0.02401462819991872 +/- 0.0015888837705011873</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>0.023120682649329528 +/- 0.0013160613360992796</t>
+          <t>0.010402275497765113 +/- 0.0018814850715628121</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.0006907761072734497 +/- 0.0004825006943127849</t>
+          <t>0.0013409183258837553 +/- 0.0007049716201908598</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.009548963835839053 +/- 0.0025064885027697953</t>
+          <t>0.015562779357984535 +/- 0.0018085504335040986</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>0.005201137748882545 +/- 0.002054323390453398</t>
+          <t>0.019057293783015017 +/- 0.0010027600714549408</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>0.004307192198293353 +/- 0.001433172863758508</t>
+          <t>-0.0008126777732629265 +/- 0.0015737437408400805</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>0.009792767167817929 +/- 0.0021612492721612545</t>
+          <t>0.0021942299878098146 +/- 0.0018726889267456973</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>0.0010158472165786026 +/- 0.0005219517504536702</t>
+          <t>0.0001219016659894323 +/- 0.0005155862470722967</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.004388459975619629 +/- 0.0031041737919194233</t>
+          <t>-0.0026818366517675886 +/- 0.002017013189108626</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.0002844372206419754 +/- 0.0015209237929470112</t>
+          <t>0.005973181633482305 +/- 0.002383585432923596</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>-0.0008939455505892035 +/- 0.0010564811052417825</t>
+          <t>0.0024786672084518126 +/- 0.0008610166639747092</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>-0.001381552214546966 +/- 0.0020814706988810535</t>
+          <t>0.0016253555465257751 +/- 0.002658338437024978</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0.007476635514018659 +/- 0.0024596092564683446</t>
+          <t>0.0018285249898414957 +/- 0.001433748782151745</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>-0.00012190166598944341 +/- 0.0010287678911964381</t>
+          <t>0.0013815522145469105 +/- 0.00087528074882317</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>-0.0004876066639577403 +/- 0.00039812917395908097</t>
+          <t>0.0004469727752945851 +/- 0.0002188201872057853</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>-0.0007314099959366161 +/- 0.0005390694498749367</t>
+          <t>-0.0006095083299471838 +/- 0.0007096403574389822</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>-0.000690776107273483 +/- 0.0005760847979991237</t>
+          <t>0.0009345794392523144 +/- 0.000728015963720784</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>0.0010158472165786026 +/- 0.0005817887469839908</t>
+          <t>0.00235676554246238 +/- 0.0013328906515121242</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.0017472572125151963 +/- 0.001348286064448374</t>
+          <t>-0.00674522551808211 +/- 0.0014216055005718054</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2616,37 +2616,37 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.0005688744412840174 +/- 0.0007536463629008927</t>
+          <t>0.0010158472165786026 +/- 0.0004892968134413657</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>-0.0020316944331572827 +/- 0.0013104035348717779</t>
+          <t>0.003941487200325033 +/- 0.001574268234685952</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.003453880536367304 +/- 0.0021211512614608997</t>
+          <t>0.004307192198293353 +/- 0.002432609434716891</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0.0023161316537992473 +/- 0.0014198622681557318</t>
+          <t>0.0014221861032100436 +/- 0.0012358314771024127</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>0.0009752133279154473 +/- 0.0012875237316338692</t>
+          <t>-0.002478667208451868 +/- 0.0016299204486088278</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>-0.0014628199918732432 +/- 0.001575840668806614</t>
+          <t>-0.002153596099146704 +/- 0.002158191259632586</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>0.014262494920763891 +/- 0.002427513536163163</t>
+          <t>0.006460788297440056 +/- 0.0018836776898007944</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.0022471910112359717 +/- 0.0011652101539741857</t>
+          <t>-0.004286308780690773 +/- 0.001454132768177797</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2666,157 +2666,157 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.0016229712858926494 +/- 0.0012267501434027254</t>
+          <t>-0.001997503121098587 +/- 0.0027716730429208024</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.003162713275072815 +/- 0.0021878384399658534</t>
+          <t>0.0005826050769871416 +/- 0.0014197854439643835</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.0013732833957553314 +/- 0.0022181036989157685</t>
+          <t>0.0032875572201415348 +/- 0.0015170808267630622</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.001539741989180199 +/- 0.0015797130999669084</t>
+          <t>-0.0020391177694548124 +/- 0.0010436900710765276</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.010070744902205586 +/- 0.0034607778420793624</t>
+          <t>-0.008281315022888026 +/- 0.003094350635875357</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.0006658343736995476 +/- 0.0002760403487603079</t>
+          <t>-0.0005409904286308387 +/- 0.00032502079383714026</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.01131918435289222 +/- 0.0031296871705306993</t>
+          <t>-0.009488139825218433 +/- 0.0020873801421530595</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.020765709529754463 +/- 0.005091463367194862</t>
+          <t>0.025593008739076183 +/- 0.004861082583061531</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.0301706200582605 +/- 0.006178759351598402</t>
+          <t>0.028381190178943028 +/- 0.005501324301177106</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>-0.0012068248023303974 +/- 0.0026414650141586933</t>
+          <t>0.0019142738243862257 +/- 0.0015593003741319325</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>-0.002871410736579272 +/- 0.0018745078035048205</t>
+          <t>-0.0017478152309612694 +/- 0.0012032319845860296</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.0076154806491884885 +/- 0.0020134782194595265</t>
+          <t>0.015522263836870632 +/- 0.002948772990105179</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.037910944652517674 +/- 0.00481886128097714</t>
+          <t>0.053932584269662964 +/- 0.0034876948547244197</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>0.01331668747399084 +/- 0.004344696840994835</t>
+          <t>0.005285060341240155 +/- 0.004860370023312304</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>-0.004369538077403268 +/- 0.0021803057673624154</t>
+          <t>-0.004993757802746535 +/- 0.001275880958531512</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-0.001081980857261755 +/- 0.0009882931408271294</t>
+          <t>-0.00374531835205989 +/- 0.0011320408246971</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.013066999583853534 +/- 0.002384777158867142</t>
+          <t>-0.005950894714939625 +/- 0.002722819442855699</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-0.004411152725759482 +/- 0.001559300374131929</t>
+          <t>-0.004535996670828113 +/- 0.0010269631859553291</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.00012484394506867558 +/- 0.0003250207938371772</t>
+          <t>-0.00024968789013728453 +/- 0.0002038693085961505</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.02559300873907615 +/- 0.002435434854498471</t>
+          <t>0.02808988764044946 +/- 0.0014801014768022279</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-0.0012484394506866558 +/- 0.0013159707283264249</t>
+          <t>-0.006200582605076954 +/- 0.0014940759942585202</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.0031210986267166006 +/- 0.0009715037478092804</t>
+          <t>-0.0018726591760299337 +/- 0.0013580664895614296</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-0.0004993757802746579 +/- 0.001231681114186332</t>
+          <t>0.0027465667915106628 +/- 0.0012920661420108353</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.0031210986267166006 +/- 0.0007267685891207904</t>
+          <t>8.322929671246148e-05 +/- 0.0011887521312597404</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.0003329171868497793 +/- 0.0007397581703966269</t>
+          <t>0.00029130253849358746 +/- 0.00037453183520600575</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>0.016229712858926347 +/- 0.0023467119733452716</t>
+          <t>0.009696213066999604 +/- 0.0013682298978588178</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0.001081980857261744 +/- 0.002107197486670353</t>
+          <t>-0.006741573033707815 +/- 0.0018592016565700112</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-0.00024968789013731787 +/- 0.0013446104387352328</t>
+          <t>0.0037453183520599676 +/- 0.0011320408246970877</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-0.0027881814398668324 +/- 0.0017062005826050867</t>
+          <t>-0.01223470661672904 +/- 0.0012372924467181604</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>-0.0006242197253433113 +/- 0.0006774373947606972</t>
+          <t>-0.0009155222638368321 +/- 0.0004482034795784144</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.000832292967124415 +/- 0.0002631941456652723</t>
+          <t>-0.0002913025384935097 +/- 0.00037453183520597984</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -2826,122 +2826,122 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.008406158967956745 +/- 0.0022778081037709485</t>
+          <t>-0.013316687473990818 +/- 0.0019430074956186178</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.008322929671244306 +/- 0.0017850695455287138</t>
+          <t>-0.00936329588014978 +/- 0.0019805250161116627</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>0.001081980857261744 +/- 0.0006500415876742904</t>
+          <t>-0.00016645859342486746 +/- 0.0004993757802746579</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>-0.0011235955056179802 +/- 0.0006186462233590787</t>
+          <t>-0.0008739076154805958 +/- 0.0006016159922930021</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>0.0019558884727423954 +/- 0.0012210903663022168</t>
+          <t>0.0016229712858926715 +/- 0.001347826445335121</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>-0.0014981273408239625 +/- 0.0007718367453596126</t>
+          <t>-0.000873907615480618 +/- 0.001398276955173662</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-4.161464835623629e-05 +/- 0.0007774257882758972</t>
+          <t>-4.161464835619189e-05 +/- 0.0003925918074097553</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.0017894298793175057 +/- 0.001696020297321242</t>
+          <t>0.003953391593841083 +/- 0.0010568809903620897</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.002330420307948411 +/- 0.0016138759408793563</t>
+          <t>-0.004161464835622108 +/- 0.0016436469128698833</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.0014148980441115234 +/- 0.0024843631388429886</t>
+          <t>0.0008322929671244706 +/- 0.0018234625301878234</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.0007490636704119757 +/- 0.0023672846697174814</t>
+          <t>0.0011652101539742499 +/- 0.0012175396453040206</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>-0.006450270495214327 +/- 0.002219664644709884</t>
+          <t>-0.003204327923429029 +/- 0.0020134782194595013</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-0.000540990428630872 +/- 0.001477759542618781</t>
+          <t>0.0011235955056180136 +/- 0.0008739076154806454</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-0.005451518934665012 +/- 0.001594986924405883</t>
+          <t>-0.00607573866000829 +/- 0.0011652101539741777</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>-0.0013316687473990951 +/- 0.00031141551284014004</t>
+          <t>0.00037453183520602673 +/- 0.00022410173978922162</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>-0.011901789429879317 +/- 0.001844238019655439</t>
+          <t>-0.0007490636704119535 +/- 0.0011135320982321962</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>-0.010819808572617584 +/- 0.0014535371782415996</t>
+          <t>0.0026633374947982124 +/- 0.001603109470183783</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-0.0029546400332917224 +/- 0.0019380992130162392</t>
+          <t>0.0008739076154806958 +/- 0.0015949869244058915</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-0.005451518934665001 +/- 0.0017000997266596245</t>
+          <t>-0.004203079483978323 +/- 0.0015284534059265172</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-0.0017894298793175167 +/- 0.0009126804910304331</t>
+          <t>-8.322929671240597e-05 +/- 0.0005520806975206476</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>-0.00024968789013732893 +/- 0.0005943760656298838</t>
+          <t>-4.161464835619189e-05 +/- 0.0006016159922930183</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>-0.00037453183520598233 +/- 0.0007074490220557799</t>
+          <t>-0.0015813566375363687 +/- 0.0005826050769871099</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-0.006034124011652098 +/- 0.001816325663153986</t>
+          <t>-0.00016645859342485637 +/- 0.001997503121098605</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-0.003620474406991292 +/- 0.0014777595426188105</t>
+          <t>0.001955888472742451 +/- 0.0024197406175791446</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2951,147 +2951,147 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>0.0006658343736995253 +/- 0.000594376065629876</t>
+          <t>0.000457761131918466 +/- 0.00034567723108273917</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>-0.012526009155222628 +/- 0.0012683937290160637</t>
+          <t>-0.01023720349563042 +/- 0.0013574287499209371</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>0.004286308780690795 +/- 0.0018892317041724726</t>
+          <t>-0.0018726591760299227 +/- 0.0016357256768234397</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>-0.0012484394506866447 +/- 0.0006446913601677091</t>
+          <t>-0.00020807324178107045 +/- 0.0003355080211526478</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-0.004660840615896822 +/- 0.0014865227714932758</t>
+          <t>-0.0017478152309612694 +/- 0.0009453030954307623</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-0.0004993757802746357 +/- 0.001273163424118053</t>
+          <t>0.0042030794839784 +/- 0.0021818937542935346</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-0.008697461506450288 +/- 0.0023278179394002536</t>
+          <t>-0.0014565126924677152 +/- 0.0011807125226060097</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-0.011776945484810664 +/- 0.002225897481534133</t>
+          <t>-0.0008322929671243928 +/- 0.0012061070949803973</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
+          <t>0.00020807324178112596 +/- 0.00033550802115269606</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>-0.005659592176446082 +/- 0.0011652101539741842</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>-0.0017894298793174723 +/- 0.0005280306924864484</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>-0.0004993757802746023 +/- 0.0007628091044454305</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>0.001290054099042892 +/- 0.0010601530755603038</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>0.0016229712858926715 +/- 0.0009926642065648246</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>0.0024552642530170864 +/- 0.0010923349769793407</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>-0.0004161464835621631 +/- 0.0002631941456652723</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>0.0001248439450687089 +/- 0.000418222039996703</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>-8.322929671239487e-05 +/- 0.0005197667913772879</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>-0.001831044527673753 +/- 0.0011041613950413347</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>-0.0009155222638368654 +/- 0.0011135320982321648</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>-0.00033291718684976825 +/- 0.0006116079257885723</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>0.0004993757802746579 +/- 0.0016520543688122627</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>-0.007074490220557661 +/- 0.0016645859342488607</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>-0.0009987515605493047 +/- 0.001072334475799009</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>0.00012484394506867558 +/- 0.0002664637635219906</t>
-        </is>
-      </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>-0.0007490636704119869 +/- 0.0010658550540878402</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>0.00041614648356221864 +/- 0.0006710160423053301</t>
-        </is>
-      </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>0.0006242197253433557 +/- 0.0006242197253433187</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>-0.0017062005826050442 +/- 0.0008817985892807782</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
         <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>0.0011652101539741944 +/- 0.0007628091044454197</t>
-        </is>
-      </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>-0.0038285476487723734 +/- 0.0015987825811318113</t>
-        </is>
-      </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>-0.0008739076154806402 +/- 0.0005409904286308916</t>
+          <t>0.00020807324178113707 +/- 0.00046526591292129246</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>-0.004036620890553478 +/- 0.0011174133651350388</t>
+          <t>0.0005826050769871305 +/- 0.0008964069591567928</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>-0.0094881398252185 +/- 0.0012456620513604483</t>
+          <t>-0.0012900540990428365 +/- 0.0009202390506656824</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>-0.002663337494798179 +/- 0.0006228310256802238</t>
+          <t>0.00020807324178115927 +/- 0.0007502187422938011</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>-0.005909280066583445 +/- 0.001821562099728634</t>
+          <t>-0.002496878901373256 +/- 0.0010193465429809293</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>-0.007990012484394526 +/- 0.002570694167537315</t>
+          <t>-0.00033291718684974603 +/- 0.001486522771493266</t>
         </is>
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>-0.0028297960882230576 +/- 0.001273163424118036</t>
+          <t>-0.005534748231377407 +/- 0.0012491328356057682</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-0.000839278220730133 +/- 0.001524624601308014</t>
+          <t>-0.0018883759966429325 +/- 0.0008445074191144914</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3111,157 +3111,157 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-0.0004616030214015576 +/- 0.0008691697514564773</t>
+          <t>-0.001510700797314346 +/- 0.0014560932918923643</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-0.0003357112882920399 +/- 0.00104151688174494</t>
+          <t>-0.0033571128829207432 +/- 0.0008180272215534063</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-0.004993705413344496 +/- 0.0015973870172617832</t>
+          <t>0.002727654217373021 +/- 0.00193444071701488</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.00016785564414605324 +/- 0.0013943136991889137</t>
+          <t>0.0018883759966428215 +/- 0.0007794450533364132</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.00637851447754928 +/- 0.0012974926423617546</t>
+          <t>-0.0031892572387746897 +/- 0.001627420850160746</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.00012589173310950663 +/- 0.00019230279878116417</t>
+          <t>-1.1102230246251566e-17 +/- 0.00018766831535877002</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.0052454888795635535 +/- 0.0010149716007090135</t>
+          <t>-0.0009651699538397284 +/- 0.001078888806729551</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.005707091900965189 +/- 0.002433906840117501</t>
+          <t>0.008392782207301663 +/- 0.0016785564414603298</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.023331934536298816 +/- 0.0023901016980106054</t>
+          <t>0.010994544691565222 +/- 0.0017584831590228313</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-0.002517834662190477 +/- 0.0010616123072323652</t>
+          <t>-0.0044062106588334425 +/- 0.0011142188877341186</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>4.1963911036535516e-05 +/- 0.0007611564056742166</t>
+          <t>-0.003692824171212805 +/- 0.0013506904691087751</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-0.00209819555182541 +/- 0.0010106248072842957</t>
+          <t>-0.0033151489718842185 +/- 0.0011173753215018422</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-0.00012589173310947332 +/- 0.001819995672866268</t>
+          <t>0.0062526227444397505 +/- 0.002722484529300633</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.006294586655476308 +/- 0.0018000512454491896</t>
+          <t>0.010113302559798542 +/- 0.00180444817456988</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>-0.001762484263533337 +/- 0.001337589378976845</t>
+          <t>0.00012589173310948443 +/- 0.0009760556734882901</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-0.00255979857322699 +/- 0.0006350292048015731</t>
+          <t>-5.551115123125783e-17 +/- 0.0008600042606764235</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>-0.0002517834662190244 +/- 0.0013296667660725877</t>
+          <t>-0.002937473772555643 +/- 0.001078072394348731</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>0.000587494754511142 +/- 0.0009787581862937772</t>
+          <t>-0.0007973143096937085 +/- 0.0009087875714522929</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.00012589173310953994 +/- 0.00019230279878121507</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.005874947545111231 +/- 0.001327015384040432</t>
+          <t>0.008434746118338166 +/- 0.0021921876435768146</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>-0.0012169534200587196 +/- 0.0010009954210555359</t>
+          <t>-0.0031053294167016966 +/- 0.0012191220349419987</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>0.001216953420058775 +/- 0.0012082400376741788</t>
+          <t>0.008015107007973098 +/- 0.00084866757936033</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.0010071338648762306 +/- 0.0015498267152848897</t>
+          <t>0.0015946286193872727 +/- 0.0011689792930914262</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.0014687368862778215 +/- 0.0012483822728194234</t>
+          <t>0.0037767519932857207 +/- 0.0006501021143445182</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.00012589173310949552 +/- 0.0005949411195450177</t>
+          <t>0.0016365925304237749 +/- 0.0006066652242887264</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>0.0033151489718842076 +/- 0.0009832458677179782</t>
+          <t>0.0029374737725555767 +/- 0.0010616123072323563</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-0.009315988250104879 +/- 0.0019931753398301304</t>
+          <t>-0.004406210658833454 +/- 0.0019253159457749743</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>-0.0008812421317666574 +/- 0.00133297357736203</t>
+          <t>0.0019303399076793348 +/- 0.0020575158492876695</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-0.0020142677297523837 +/- 0.001310994490290678</t>
+          <t>0.0009232060428031264 +/- 0.0008137104250803682</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>0.0009651699538397174 +/- 0.00037767519932858777</t>
+          <t>0.0003776751993285532 +/- 0.0003485784247972245</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.0007133864876206597 +/- 0.00037767519932857297</t>
+          <t>0.0005874947545110865 +/- 0.0008434641729853693</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -3271,122 +3271,122 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.0015107007973143237 +/- 0.001048258161711867</t>
+          <t>0.0014267729752412417 +/- 0.0012334820358119284</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.009987410826689035 +/- 0.0019664917354360084</t>
+          <t>0.0021821233738984146 +/- 0.0010244696278416932</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>0.0003357112882920732 +/- 0.0005241290808559206</t>
+          <t>0.0008812421317666464 +/- 0.0006350292048015534</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>-0.0005455308434745732 +/- 0.0004616030214015728</t>
+          <t>-0.00041963911036513313 +/- 0.0008180272215534291</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-0.0015526647083507928 +/- 0.0012872733235566743</t>
+          <t>-0.0010490977759127662 +/- 0.0008852296730897649</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>-0.0003776751993285643 +/- 0.0010524495345349903</t>
+          <t>0.0006714225765840798 +/- 0.0010649246781745145</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-0.000545530843474551 +/- 0.0004616030214015889</t>
+          <t>4.1963911036480005e-05 +/- 0.0004381160935338139</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.0016365925304238748 +/- 0.0007611564056742405</t>
+          <t>0.002266051195971419 +/- 0.0008842344735923441</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.0013008812421317017 +/- 0.0012227278459365093</t>
+          <t>0.0033990767939571453 +/- 0.0011787303319503357</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>-0.0026017624842635144 +/- 0.0008350712858637202</t>
+          <t>0.001468736886277744 +/- 0.001065751162333211</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-0.005161561057490538 +/- 0.0013668902622662443</t>
+          <t>-0.0014267729752413417 +/- 0.0009605978298161557</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>4.196391103654662e-05 +/- 0.0009467489863766948</t>
+          <t>0.004070499370541292 +/- 0.001011495660360387</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.0007133864876206708 +/- 0.0007280466459461754</t>
+          <t>0.0025178346621904657 +/- 0.0006501021143445182</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>0.0007133864876206819 +/- 0.001062441368121877</t>
+          <t>0.0015946286193872727 +/- 0.0009715347799236423</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>0.0006294586655476442 +/- 0.00043000213033821176</t>
+          <t>-0.00016785564414605324 +/- 0.00027835709528793723</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>-0.0020142677297523837 +/- 0.0010415168817449294</t>
+          <t>0.00020981955518249994 +/- 0.001014971600709002</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.00012589173310956214 +/- 0.0012313387118020429</t>
+          <t>0.0039026437263952494 +/- 0.0010788888067295387</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-0.02568191355434324 +/- 0.002983867198427376</t>
+          <t>-0.0006294586655476664 +/- 0.0017529667288464596</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-0.010616869492236624 +/- 0.0015929712879649402</t>
+          <t>0.00579101972303816 +/- 0.001676456932894519</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-8.392782207299332e-05 +/- 0.0005241290808559047</t>
+          <t>0.0012169534200587085 +/- 0.000512234813920832</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>-0.0005455308434745732 +/- 0.0005324623390872519</t>
+          <t>0.00016785564414599773 +/- 0.00027835709528788703</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.0008392782207301775 +/- 0.0003250510571722627</t>
+          <t>8.392782207300442e-05 +/- 0.00016785564414600884</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-0.019093579521611382 +/- 0.0012900063910146408</t>
+          <t>-0.0018883759966429325 +/- 0.0018696323466173398</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-0.00020981955518252217 +/- 0.0013949450389085</t>
+          <t>0.002056231640788886 +/- 0.0017143682933961958</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3396,147 +3396,147 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>-0.0020562316407889193 +/- 0.00022598257688353203</t>
+          <t>0.0034410407049936587 +/- 0.00045196515376705576</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>-0.005581200167855638 +/- 0.0012872733235566906</t>
+          <t>0.004280318925723825 +/- 0.0014872047961955125</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>-0.003902643726395283 +/- 0.0011876602348371928</t>
+          <t>0.002224087284934917 +/- 0.0014542780907397094</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>-0.0009651699538396508 +/- 0.0006779477306505968</t>
+          <t>0.0010910616869491685 +/- 0.0006818328497386373</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-0.0034410407049936696 +/- 0.001007133864876216</t>
+          <t>0.002685690306336508 +/- 0.0011446228868640964</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-0.02748636172891309 +/- 0.002238293806646191</t>
+          <t>-0.0057910197230382375 +/- 0.0011987290689958656</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-0.0016365925304238083 +/- 0.0015066154486795054</t>
+          <t>0.0024339068401174613 +/- 0.0011689792930914128</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-0.009232060428031852 +/- 0.0012162296891472448</t>
+          <t>0.00906420478388582 +/- 0.0016274208501607392</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>-0.0003776751993285199 +/- 0.00012589173310950663</t>
+          <t>-0.0007973143096937418 +/- 0.00022598257688353203</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>0.0004616030214016242 +/- 0.0019362605111304105</t>
+          <t>-0.001007133864876253 +/- 0.0009787581862937859</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>-0.003483004616030205 +/- 0.0009392794496684698</t>
+          <t>0.00025178346621899104 +/- 0.001081334345507778</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0.0010071338648762417 +/- 0.0004672903367880946</t>
+          <t>0.00016785564414598664 +/- 0.0006280583108307293</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>0.0007553503986571953 +/- 0.0021298493563490606</t>
+          <t>0.0014267729752412638 +/- 0.0017117984099346412</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>-0.004490138480906391 +/- 0.0010457352743917002</t>
+          <t>-0.0014267729752413417 +/- 0.001081334345507766</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
         <is>
-          <t>-0.003986571548468288 +/- 0.0016494539661798978</t>
+          <t>0.00243390684011745 +/- 0.0012561166216614051</t>
         </is>
       </c>
       <c r="BX7" t="inlineStr">
         <is>
+          <t>0.0007973143096936086 +/- 0.00043811609353378624</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>0.0003776751993285421 +/- 0.0006882593145974267</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>0.00243390684011745 +/- 0.000556714190575851</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="BY7" t="inlineStr">
-        <is>
-          <t>0.0008812421317666907 +/- 0.0003485784247972433</t>
-        </is>
-      </c>
-      <c r="BZ7" t="inlineStr">
-        <is>
-          <t>0.00020981955518255545 +/- 0.00038688814340296393</t>
-        </is>
-      </c>
-      <c r="CA7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>-0.0013428451531682373 +/- 0.000616741017905966</t>
+          <t>0.000839278220730122 +/- 0.0006766477338059846</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>-0.0015107007973142795 +/- 0.0006554972451453707</t>
+          <t>0.0028115820394460146 +/- 0.0011423128484109447</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>0.000419639110365122 +/- 0.00018766831535877002</t>
+          <t>0.00020981955518252217 +/- 0.00028150247303814266</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>0.0005035669324381375 +/- 0.0005874947545111261</t>
+          <t>0.0014267729752412306 +/- 0.0010141037325719267</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>-0.001133025597985704 +/- 0.0010624413681218769</t>
+          <t>-0.0037767519932858096 +/- 0.0011869186423609731</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>-0.001468736886277766 +/- 0.0015275094186488745</t>
+          <t>-0.0019303399076794348 +/- 0.0008223213572079314</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>0.0002937473772555821 +/- 0.000594941119545014</t>
+          <t>-0.0003357112882921176 +/- 0.0006971568495944731</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>-0.003147293327738132 +/- 0.0012053215792148671</t>
+          <t>-0.0021821233738984814 +/- 0.0014512477100957412</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>0.003189257238774701 +/- 0.0015611477329197116</t>
+          <t>0.00327318506084765 +/- 0.0012561166216614155</t>
         </is>
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>-0.005874947545111165 +/- 0.0010279016965099564</t>
+          <t>-0.009777591271506547 +/- 0.0009939336367878328</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.0034148397976391355 +/- 0.0011991115222030242</t>
+          <t>0.0001686340640809192 +/- 0.0005059021922428408</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3556,157 +3556,157 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-4.21585160202298e-05 +/- 0.0006652501618068992</t>
+          <t>0.0021079258010117787 +/- 0.0010497385833042592</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-0.0006745362563237767 +/- 0.001730040854020519</t>
+          <t>-2.2204460492503132e-17 +/- 0.0007541544612140873</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-0.010455311973018544 +/- 0.0010292205409556388</t>
+          <t>-0.002318718381112994 +/- 0.0010196784673227593</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-0.0033726812816188946 +/- 0.0012787311035500153</t>
+          <t>0.0010539629005058893 +/- 0.0009091002804742027</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.005185497470489031 +/- 0.0012370489672108964</t>
+          <t>0.0002107925801011823 +/- 0.0014755480607082571</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-8.43170320404818e-05 +/- 0.0002529510961214454</t>
+          <t>8.43170320404596e-05 +/- 0.0001686340640809192</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.008178752107925801 +/- 0.0011804384485666246</t>
+          <t>-0.0008431703204047402 +/- 0.0008639924760505466</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-0.03878583473861722 +/- 0.0040830691442844185</t>
+          <t>-0.01800168634064083 +/- 0.00339395692454955</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.05113827993254637 +/- 0.0036610004789822117</t>
+          <t>-0.014376053962900514 +/- 0.002454262997947364</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.0007166947723439953 +/- 0.000731422916226715</t>
+          <t>0.0017284991568296548 +/- 0.00115378854834771</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>-0.00016863406408095248 +/- 0.0006585370721675299</t>
+          <t>-0.0011382799325463711 +/- 0.0008650204270102344</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-0.00497470489038786 +/- 0.0012042880992483773</t>
+          <t>0.001096121416526108 +/- 0.0013089523352664445</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.015556492411467105 +/- 0.002553637052429636</t>
+          <t>0.023355817875210794 +/- 0.00260701936488031</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.0004637436762226055 +/- 0.0025185964639534387</t>
+          <t>0.013996627318718369 +/- 0.002943860075901529</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>-0.0009696458684654407 +/- 0.0015553007374112015</t>
+          <t>-0.004089376053962901 +/- 0.0011781777919462248</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>-0.0013069139966273347 +/- 0.001339155158032782</t>
+          <t>-0.0005059021922428463 +/- 0.0005592959174292196</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>-0.0038364249578415 +/- 0.0014165512324124474</t>
+          <t>0.003794266441821237 +/- 0.001423435330196792</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>-0.0009274873524451998 +/- 0.0008598683834052013</t>
+          <t>0.0018549747048903886 +/- 0.00168844725080107</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.00026663386679331703</t>
+          <t>0.0001686340640809192 +/- 0.00020653370512502638</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-0.0034148397976391355 +/- 0.001391231028667793</t>
+          <t>0.005522765598650925 +/- 0.001057330202696825</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>0.0009696458684654297 +/- 0.0011001676518296681</t>
+          <t>0.002655986509274855 +/- 0.0005349315995130374</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>-0.0038364249578415 +/- 0.0010573302026968387</t>
+          <t>0.0002107925801011601 +/- 0.0008691200728536514</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>-0.0005059021922428353 +/- 0.0008174839557194558</t>
+          <t>0.0002951096121416308 +/- 0.0005977001213641753</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.005227655986509261 +/- 0.00106986319902608</t>
+          <t>0.001433389544688002 +/- 0.0005718659344962265</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.00029510961214166407 +/- 0.000379426644182136</t>
+          <t>4.215851602019649e-05 +/- 0.0003501949351988989</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>0.00202360876897133 +/- 0.0014701176875347858</t>
+          <t>0.0010118043844856706 +/- 0.0013621833407591434</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-0.0019392917369308593 +/- 0.0011185918348584928</t>
+          <t>0.00223440134907249 +/- 0.002141801989187271</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>0.001053962900505878 +/- 0.0011193860073652282</t>
+          <t>-0.00042158516020238677 +/- 0.0007541544612140748</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>8.43170320404707e-05 +/- 0.0009576573938955007</t>
+          <t>0.006365935919055654 +/- 0.001783160706792299</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>-0.0004637436762226055 +/- 0.00044014782921208186</t>
+          <t>0.0006323777403035025 +/- 0.00028280792295531763</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.00016863406408095248 +/- 0.000337268128161905</t>
+          <t>-0.0001264755480607338 +/- 0.00026994621574338303</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -3716,122 +3716,122 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.001433389544688035 +/- 0.0011025882656510862</t>
+          <t>0.0013490725126475422 +/- 0.0009576573938955045</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.0022344013490725235 +/- 0.0017181858239725652</t>
+          <t>0.005269814502529513 +/- 0.001336498101530137</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>0.0001264755480607227 +/- 0.0001931945908497623</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>-1.1102230246251566e-17 +/- 0.000461823404304557</t>
+          <t>0.00025295109612136766 +/- 0.0004694573661745438</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>0.000295109612141653 +/- 0.0010838920853442227</t>
+          <t>-0.0016441821247892064 +/- 0.0010573302026968367</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>0.000590219224283306 +/- 0.000983297115488251</t>
+          <t>0.003246205733558183 +/- 0.0013204434876362544</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>0.0001686340640809414 +/- 0.0004299341917026099</t>
+          <t>0.0005480607082630317 +/- 0.00032926853608377353</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.0019814502529511002 +/- 0.0008442236254005411</t>
+          <t>-0.0001686340640809858 +/- 0.0009832971154882404</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.0009274873524451888 +/- 0.0010797848629734836</t>
+          <t>0.003541315345699825 +/- 0.0009081222271727761</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>-0.0057335581787521074 +/- 0.0014749456732323738</t>
+          <t>-0.0007166947723440176 +/- 0.0010505848055967024</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-0.041273187183811136 +/- 0.001783160706792299</t>
+          <t>-0.010792580101180449 +/- 0.0006309708915301661</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>-0.001222596964586875 +/- 0.0006094785959022179</t>
+          <t>0.000252951096121401 +/- 0.0008680969764744669</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-0.0015598650927487246 +/- 0.0012654579274707842</t>
+          <t>0.001433389544688013 +/- 0.0009081222271727741</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>0.0017706576728499068 +/- 0.001317074144335025</t>
+          <t>-0.0001686340640809636 +/- 0.0005718659344962282</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>0.00033726812816190497 +/- 0.0003154854457650882</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>-0.001728499156829677 +/- 0.0007166947723440026</t>
+          <t>0.0033726812816188946 +/- 0.0009613620784984276</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>-0.01083473861720068 +/- 0.0011001676518296625</t>
+          <t>-0.0001686340640809858 +/- 0.0010863489651538848</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-0.037942664418212466 +/- 0.0023472868308727093</t>
+          <t>-0.0016863406408094584 +/- 0.0016108746352902843</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-0.02415682967959528 +/- 0.0017891311276494852</t>
+          <t>-0.00999156829679596 +/- 0.0010335287244629908</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-0.0005902192242833171 +/- 0.00046945736617454186</t>
+          <t>-0.0009696458684654519 +/- 0.00032926853608375504</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>-0.0004637436762225944 +/- 0.0006914510736448815</t>
+          <t>-0.0001686340640809636 +/- 0.00020653370512508076</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.0011804384485666342 +/- 0.00016863406408096357</t>
+          <t>-0.000421585160202409 +/- 0.0</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-0.008726812816188857 +/- 0.001373229129418408</t>
+          <t>-0.00969645868465432 +/- 0.0014234353301968085</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-0.015472175379426656 +/- 0.0020829037650987483</t>
+          <t>-0.009190556492411484 +/- 0.0019208744940800231</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3841,147 +3841,147 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0001885386153035451</t>
+          <t>-0.0001264755480607227 +/- 0.00019319459084976234</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>-0.0013490725126475422 +/- 0.0007954452893808055</t>
+          <t>0.0006745362563237656 +/- 0.0006849948064617183</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>-0.022554806070826317 +/- 0.001388673616526191</t>
+          <t>-0.003836424957841489 +/- 0.0008098386472301178</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>-0.001222596964586853 +/- 0.0003977226446903975</t>
+          <t>0.000548060708263054 +/- 0.0005977001213641643</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-0.0003794266441821237 +/- 0.00112255707889498</t>
+          <t>-0.00033726812816190497 +/- 0.0008174839557194478</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-0.038870151770657654 +/- 0.0011894381095839649</t>
+          <t>-0.002403035413153465 +/- 0.001485153031518419</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-0.013617200674536267 +/- 0.0017181858239725845</t>
+          <t>-0.0016020236087689655 +/- 0.0010631973198076043</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-0.0035834738617200766 +/- 0.0008691200728536407</t>
+          <t>0.000843170320404707 +/- 0.0004988262886256195</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
+          <t>4.21585160202298e-05 +/- 0.0001264755480606894</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>0.0017284991568296659 +/- 0.0005480607082630796</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>-0.0001264755480607227 +/- 0.00032926853608374935</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>-0.0002107925801012045 +/- 0.0002107925801012045</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>0.0005902192242832838 +/- 0.0009274873524451948</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>0.0024030354131534203 +/- 0.0007067055065025237</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>0.0003372681281618828 +/- 0.0007954452893808186</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>4.21585160202298e-05 +/- 0.00012647554806068939</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>-0.0002529510961214454 +/- 0.00020653370512508076</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>0.0001264755480606672 +/- 0.0005006046411061386</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>-0.004258010118043854 +/- 0.0009322657836212245</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>-0.001981450252951089 +/- 0.0008442236254005338</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>-1.1102230246251566e-17 +/- 0.0005332677335865815</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>-0.0015177065767285058 +/- 0.0011954002427283035</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>-0.0036677908937605254 +/- 0.0011162059270551149</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>8.43170320404707e-05 +/- 0.0005265596963236509</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>-0.00021079258010119338 +/- 0.0002828079229552928</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>-0.0008431703204047514 +/- 0.0003770772306070406</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>-0.0005480607082630872 +/- 0.000269946215743357</t>
-        </is>
-      </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>0.0002951096121416308 +/- 0.00037942664418212494</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>0.00033726812816186057 +/- 0.0007003898703978258</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
         <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>0.0003372681281619272 +/- 0.00016863406408096357</t>
-        </is>
-      </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>-0.001180438448566623 +/- 0.0007003898703978059</t>
-        </is>
-      </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>-0.00025295109612142317 +/- 0.0003863891816994908</t>
+          <t>0.00042158516020233126 +/- 0.0003265584608943802</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>-0.0008853288364249589 +/- 0.0011225570788949855</t>
+          <t>0.000548060708263054 +/- 0.0011320169968041796</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>0.0026559865092748657 +/- 0.0008853288364249553</t>
+          <t>-0.0027824620573355997 +/- 0.0007588532883642511</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>-0.00042158516020238677 +/- 0.00026663386679328196</t>
+          <t>0.00037942664418209036 +/- 0.00029510961214164347</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>0.001728499156829677 +/- 0.001242782712730501</t>
+          <t>0.001981450252951078 +/- 0.0005671848249187925</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>0.0002951096121416752 +/- 0.0005349315995130549</t>
+          <t>0.0017706576728498957 +/- 0.001174400360639497</t>
         </is>
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>0.0011382799325463822 +/- 0.0006544761676332086</t>
+          <t>-4.2158516020263105e-05 +/- 0.0006652501618068901</t>
         </is>
       </c>
     </row>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.0026161655603279764 +/- 0.0023235572896231063</t>
+          <t>0.0157360406091371 +/- 0.0018067528779787977</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4001,157 +4001,157 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-0.003123779773525992 +/- 0.0012347823741383757</t>
+          <t>0.007809449433814975 +/- 0.0022362859919213265</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.009605622803592317 +/- 0.00251362388745508</t>
+          <t>0.011557985162046114 +/- 0.0017127459741867412</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-0.005388520109332306 +/- 0.002049887504632044</t>
+          <t>0.0032018742678641687 +/- 0.0021444014397104384</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-0.0007418976962124457 +/- 0.002866450941387409</t>
+          <t>0.008043732916829405 +/- 0.002370010293712371</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.011518937914876948 +/- 0.0025017678218885423</t>
+          <t>0.0037875829754002834 +/- 0.00261383334184764</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.0007028504490433907 +/- 0.000382583325698297</t>
+          <t>0.0009761811792269204 +/- 0.0007252704264352413</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.003045685279187804 +/- 0.0015001462485199801</t>
+          <t>0.007458024209293301 +/- 0.001190140621173612</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.028114017961733663 +/- 0.0031625859791201195</t>
+          <t>0.04006247559547057 +/- 0.0034049557761174007</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.041897696212417 +/- 0.0040392673915423715</t>
+          <t>0.03342444357672788 +/- 0.0042602676132716365</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.0019133151112846192 +/- 0.0017931999224060783</t>
+          <t>0.00991800078094498 +/- 0.002045419891246986</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.0027333073018352082 +/- 0.0008002304385755203</t>
+          <t>0.012260835611089472 +/- 0.0027510995632656662</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.011440843420538837 +/- 0.0007819205152089294</t>
+          <t>0.018469347910972322 +/- 0.0021883883278722414</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.05298711440843418 +/- 0.005588123560076256</t>
+          <t>0.037212026552128116 +/- 0.004724716907458024</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.02709878953533773 +/- 0.002964506504662609</t>
+          <t>0.013822725497852451 +/- 0.002567634864939247</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.009800859039437693 +/- 0.0025691189612801367</t>
+          <t>0.011050370948848153 +/- 0.0017114101523475972</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.013549394767668855 +/- 0.00225021937278</t>
+          <t>0.007145646231940694 +/- 0.0016009371339320729</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.003514252245216698 +/- 0.002407033972264335</t>
+          <t>0.00901991409605627 +/- 0.0013688831037062163</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.004998047637641512 +/- 0.0031471209183303217</t>
+          <t>0.0201874267864116 +/- 0.002637062710644763</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-0.0002733307301835408 +/- 0.0002500243747533498</t>
+          <t>-0.00015618898867626464 +/- 0.0003982053505343632</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.01608746583365871 +/- 0.0020349573167973934</t>
+          <t>0.02139789144865294 +/- 0.0028146538525482346</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0.012495119094103835 +/- 0.002766573929546026</t>
+          <t>0.0055447090980086265 +/- 0.0014899479912798877</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>-0.007536118703631423 +/- 0.0019683066241512662</t>
+          <t>-0.0031237797735259366 +/- 0.0020587936472415444</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>-0.00882467786021086 +/- 0.001747991353814868</t>
+          <t>-0.009878953533775835 +/- 0.0020739198320795893</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.006130417805544741 +/- 0.0012229956863229858</t>
+          <t>-0.0025380710659898 +/- 0.0011616145865399052</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.0013666536509176486 +/- 0.0008237025814029346</t>
+          <t>0.0003123779773526403 +/- 0.0006487015902317773</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>-0.016243654822335064 +/- 0.0019224574189911788</t>
+          <t>-0.010620851229988227 +/- 0.003058673335035697</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-0.008356110894181989 +/- 0.0028330116590733418</t>
+          <t>-0.003592346739554819 +/- 0.0012926938974811987</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>0.010386567746973807 +/- 0.0024707992221095626</t>
+          <t>0.022061694650527163 +/- 0.002822497519484753</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.019601718078875407 +/- 0.002367435594099822</t>
+          <t>0.011323701679031661 +/- 0.0012832234849789203</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>3.9047247169055054e-05 +/- 0.0006161551674369347</t>
+          <t>-0.00023428348301439693 +/- 0.0005296626304666277</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.0005466614603670594 +/- 0.0012123525729215384</t>
+          <t>0.0019523623584537409 +/- 0.0007809449433814896</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -4161,122 +4161,122 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.010035142522452134 +/- 0.001720296038415525</t>
+          <t>0.015696993361968038 +/- 0.001735736881756562</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.009488481062085075 +/- 0.0026196599949581383</t>
+          <t>0.001952362358453763 +/- 0.0024509730302967945</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>-0.00015618898867632015 +/- 0.0005296626304666523</t>
+          <t>-0.0013276064037484937 +/- 0.00043481174250917573</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>-0.0013276064037485713 +/- 0.001050653966971787</t>
+          <t>0.001288559156579494 +/- 0.0009885973370692823</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-0.00898086684888717 +/- 0.002036455261289394</t>
+          <t>-0.004060913705583702 +/- 0.002476962362694832</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>0.006559937524404491 +/- 0.0025473653151581537</t>
+          <t>0.015696993361968038 +/- 0.0015793634061817172</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-0.0012104646622413616 +/- 0.001054275673565005</t>
+          <t>0.004295197188598254 +/- 0.0008904142327990171</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.010230378758297553 +/- 0.0018464022518605064</t>
+          <t>0.0022256930886372928 +/- 0.0015913849177910844</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.012573213588442 +/- 0.0028842148086871354</t>
+          <t>0.0151112846544319 +/- 0.0024944437725395617</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.00031237797735256256 +/- 0.0017357368817565886</t>
+          <t>0.00160093713393209 +/- 0.0019944697835411283</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-0.015306520890277276 +/- 0.0013616240354676107</t>
+          <t>-0.008629441624365464 +/- 0.0020398216144645012</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>0.011870363139398632 +/- 0.0032911062094034553</t>
+          <t>0.011284654431862606 +/- 0.00224615025666064</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.0012885591565794275 +/- 0.0012956392052352248</t>
+          <t>0.004646622413119928 +/- 0.0017060564056972718</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>0.0024209293244826014 +/- 0.0018710110973386858</t>
+          <t>0.009058961343225347 +/- 0.0012073115840484333</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>-0.0003123779773526403 +/- 0.0009532647884212266</t>
+          <t>0.0015618898867630127 +/- 0.0006984983920343004</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>-0.0006638032018743023 +/- 0.0028051581500448093</t>
+          <t>0.0006247559547052251 +/- 0.0015143084287126281</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>-0.004178055447091022 +/- 0.0024883239307075086</t>
+          <t>0.002303787582975425 +/- 0.0031259754095471037</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-0.0041390081999219345 +/- 0.0016212838338169938</t>
+          <t>0.00605232331120662 +/- 0.003249378558589084</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-0.003631393986723963 +/- 0.0019527527918859764</t>
+          <t>-0.008473252635689144 +/- 0.002153270703469298</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-0.0010542756735650415 +/- 0.000838379951330892</t>
+          <t>0.0009761811792269093 +/- 0.0008599264172411298</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.0006638032018742579 +/- 0.0009411925648726263</t>
+          <t>0.002459976571651734 +/- 0.0010189760523779774</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.0010933229207340522 +/- 0.00015618898867630904</t>
+          <t>0.0012495119094104502 +/- 0.0004205517225407574</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>0.011948457633736798 +/- 0.0027896245372107456</t>
+          <t>0.005505661850839572 +/- 0.00239719570139332</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>0.007536118703631345 +/- 0.0020665550366886663</t>
+          <t>-0.002577118313158877 +/- 0.00196946820974906</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4286,92 +4286,92 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>-0.0011323701679032071 +/- 0.0006404224703966002</t>
+          <t>0.0002733307301835741 +/- 0.0008199921905505796</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>-0.0026942600546661978 +/- 0.001164236744699382</t>
+          <t>0.005583756345177715 +/- 0.0014298971826318075</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>-0.010542756735650171 +/- 0.0017893696583193505</t>
+          <t>0.0009761811792269093 +/- 0.0023895511567035227</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.0007418976962123902 +/- 0.000947650222531165</t>
+          <t>-0.002108551347129994 +/- 0.000500048749506651</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.0015618898867629572 +/- 0.0013526363198507437</t>
+          <t>0.010698945724326493 +/- 0.002990111631249781</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-0.00628660679422105 +/- 0.0017588606996571865</t>
+          <t>-0.002381882077313502 +/- 0.0020398216144645186</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>0.0035532994923857643 +/- 0.0020841868246907445</t>
+          <t>0.015970324092151544 +/- 0.0020621235340118637</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>0.011479890667707882 +/- 0.0009909080468918172</t>
+          <t>0.01151893791487706 +/- 0.0014636208367037127</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>-0.00042951971885984985 +/- 0.00021027586127039726</t>
+          <t>0.0005466614603670594 +/- 0.0006344426711937505</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>0.008199921905505624 +/- 0.002804886371896593</t>
+          <t>0.012846544318625596 +/- 0.0016880879594859204</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.0029675907848496384 +/- 0.002075022296850675</t>
+          <t>0.007926591175322217 +/- 0.001562377901112255</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>0.0014447481452557365 +/- 0.0009082158023906966</t>
+          <t>0.0008199921905506002 +/- 0.0008634652240334236</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>0.017258883248730938 +/- 0.0013838379653783113</t>
+          <t>0.023272159312768482 +/- 0.00214724358998321</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>-0.004998047637641567 +/- 0.0015402641876857202</t>
+          <t>0.013080827801640016 +/- 0.002000576096438796</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
         <is>
-          <t>0.009371339320577866 +/- 0.001118142995960671</t>
+          <t>0.015072237407262833 +/- 0.0013991778888847368</t>
         </is>
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>7.809449433815452e-05 +/- 0.00023428348301446356</t>
+          <t>0.00035142522452169533 +/- 0.00032435079511591744</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>-0.0007028504490433684 +/- 0.0008696234850183784</t>
+          <t>0.0003123779773526292 +/- 0.0009532647884212121</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>-0.0021085513471300723 +/- 0.0006808120177338025</t>
+          <t>0.0019133151112846857 +/- 0.0008087588901682172</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>-0.001132370167903196 +/- 0.0005076142131979583</t>
+          <t>0.0010152284263959977 +/- 0.0009436193653724667</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>-0.0010152284263959532 +/- 0.0017392469700367235</t>
+          <t>0.008395158141351089 +/- 0.002318301852213562</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4396,37 +4396,37 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>0.00031237797735259585 +/- 0.0003404060088668943</t>
+          <t>0.003709488481062129 +/- 0.0005857087075361404</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>0.007692307692307676 +/- 0.0026486009968155534</t>
+          <t>0.00925419757907071 +/- 0.0020443014623519537</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>0.0019133151112846413 +/- 0.0024035475824306838</t>
+          <t>0.0021866458414682155 +/- 0.0016492551411122851</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>-0.0007418976962124457 +/- 0.0008634652240334469</t>
+          <t>0.0022256930886372815 +/- 0.0006774444190900938</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>0.01073799297149548 +/- 0.002175811279305736</t>
+          <t>0.009566575556423308 +/- 0.0024772701172294975</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>0.015267473643108131 +/- 0.001566276541986079</t>
+          <t>0.029558766106989508 +/- 0.0017897956480071677</t>
         </is>
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>0.006403748535728182 +/- 0.0011343880551608003</t>
+          <t>0.005115189379148821 +/- 0.0015367956777941848</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.0005898545025560864 +/- 0.0014314018657649546</t>
+          <t>-0.0032245379473063163 +/- 0.00125343117974906</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4446,157 +4446,157 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-0.02548171451042073 +/- 0.0021595800578444167</t>
+          <t>-0.0400707825403067 +/- 0.0017973094584390668</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.01710578057412502 +/- 0.0021627998427054753</t>
+          <t>0.000865119937082226 +/- 0.0017302398741643689</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.0024380652772315716 +/- 0.0019724634217828468</t>
+          <t>0.0037357451828549217 +/- 0.0012088420093542753</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-0.00589854502556032 +/- 0.0010254349044754316</t>
+          <t>-0.007432166732206036 +/- 0.0011855928770492749</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.004954777821470735 +/- 0.001820815871457363</t>
+          <t>0.0034211561148250304 +/- 0.000825796303578442</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.00039323633503741685 +/- 0.0003932363350373835</t>
+          <t>-0.00039323633503730583 +/- 0.00017586063527327947</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.0043649233189147155 +/- 0.0021996643760829027</t>
+          <t>0.0006291781360598159 +/- 0.0020673911801958205</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-0.011246559182068372 +/- 0.0043689954895261155</t>
+          <t>-0.0042469524184034265 +/- 0.0020568929344273834</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.015847424302005465 +/- 0.0024051795019068706</t>
+          <t>-0.012780180888714077 +/- 0.00242566582985313</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.0034998033818325336 +/- 0.0013095419430080055</t>
+          <t>0.0031065670467951612 +/- 0.0017271090252455978</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>-0.016083366103027873 +/- 0.0010904777525648293</t>
+          <t>-0.011167911915060936 +/- 0.001928061450590823</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>-0.004050334250884735 +/- 0.001374078270519574</t>
+          <t>-0.008611875737318109 +/- 0.001433560844165029</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>-0.019740464018875303 +/- 0.005225162482697014</t>
+          <t>-0.015021627998427012 +/- 0.005038338144883037</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>-0.001140385371608299 +/- 0.0027886528747922044</t>
+          <t>-0.0033818324813212454 +/- 0.003964477596894544</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>-0.003932363350373525 +/- 0.001974030735039121</t>
+          <t>-0.004640188753440766 +/- 0.0012410329404687022</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>-0.007156901297679885 +/- 0.001136990349571427</t>
+          <t>-0.004168305151395946 +/- 0.0018037506789114564</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>0.010342115611482539 +/- 0.002524381257680555</t>
+          <t>0.00778607943373969 +/- 0.0018842545891798613</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>-0.0063311049941014216 +/- 0.0016065039886602717</t>
+          <t>-0.0067636649626425125 +/- 0.0015310988858774435</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.00019661816751870287 +/- 0.00019661816751870284</t>
+          <t>-0.0004325599685410686 +/- 0.000326646632438772</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-0.0010224144710970883 +/- 0.0030164072215124195</t>
+          <t>-0.0033425088478175047 +/- 0.0026800722314414137</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>-0.0019268580416829995 +/- 0.001672526175236873</t>
+          <t>-0.001572945340149401 +/- 0.0012310244469129776</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>-0.00019661816751862516 +/- 0.0009511118067202468</t>
+          <t>-0.0011797090051120396 +/- 0.0014713556377404437</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.0014156508061345496 +/- 0.001220933912407398</t>
+          <t>-0.0007471490365709377 +/- 0.0009704256924304564</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.0019661816751868288 +/- 0.001098249315278729</t>
+          <t>0.0002752654345261618 +/- 0.0007874551472473812</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.00019661816751872507 +/- 0.00036254598730999215</t>
+          <t>-0.0007078254030671971 +/- 0.0005216869509013627</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0.0036570979158474515 +/- 0.001934866629987027</t>
+          <t>0.00011797090051124393 +/- 0.0012929046183856525</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-0.00204482894219421 +/- 0.0031936988602826403</t>
+          <t>0.004482894219425914 +/- 0.0021044574377128743</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>0.00035391270153365404 +/- 0.002255202667548512</t>
+          <t>-0.002909948879276425 +/- 0.0017248692252820668</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0001572945340149734 +/- 0.002126387075831028</t>
+          <t>-0.005937868659064061 +/- 0.0017800189221795115</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>7.864726700752555e-05 +/- 0.0006041011205559517</t>
+          <t>0.00023594180102244345 +/- 0.0008097231727083568</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.0020055053086904693 +/- 0.0008332528549122003</t>
+          <t>-0.0007471490365709599 +/- 0.0007132661088170374</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -4606,122 +4606,122 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.003460479748328782 +/- 0.0009437672040896675</t>
+          <t>0.005348014156508096 +/- 0.0014734560751234877</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.001297679905623239 +/- 0.0011403853716083327</t>
+          <t>-0.003027919779787602 +/- 0.0019348666299870275</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>3.932363350376278e-05 +/- 0.0002752654345261491</t>
+          <t>-0.0007471490365709377 +/- 0.00066850176956351</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>-0.0010224144710970883 +/- 0.000503588221583386</t>
+          <t>0.0004325599685411352 +/- 0.0008695770502357655</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>0.001887534408179381 +/- 0.0013018439132714806</t>
+          <t>-0.001572945340149401 +/- 0.0011397071762634377</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>0.0018482107746756072 +/- 0.001553656804179181</t>
+          <t>-0.0024380652772315937 +/- 0.0012657079779340346</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>0.001376327172630787 +/- 0.0009010176356578376</t>
+          <t>-0.0003145890680298469 +/- 0.0009759869167118359</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.003893039716869884 +/- 0.00161610087204361</t>
+          <t>0.0033818324813213118 +/- 0.001420013376741467</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.004286276051907234 +/- 0.0015071779706438766</t>
+          <t>-0.0047974832874557284 +/- 0.0008211015736461314</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.003460479748328782 +/- 0.0020035767523172666</t>
+          <t>0.0012190326386158467 +/- 0.0017181323063274437</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.008061344868265874 +/- 0.0012952944626032743</t>
+          <t>0.017931576877703536 +/- 0.0026855479479298314</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>0.003539127015336263 +/- 0.001502553926428855</t>
+          <t>-0.0002752654345261063 +/- 0.0011671900967090787</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.00310656704679515 +/- 0.0007952712707886939</t>
+          <t>0.004089657884388554 +/- 0.0011288006366030165</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>0.009083759339363007 +/- 0.0016725261752368657</t>
+          <t>-0.0012583562721195317 +/- 0.0013599383771758257</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>3.932363350377388e-05 +/- 0.000814483491042408</t>
+          <t>0.0014942980731419975 +/- 0.0006532932648775682</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>-0.00039323633503731694 +/- 0.0006580102450130241</t>
+          <t>-0.0042469524184034265 +/- 0.0007825304263520532</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.0010224144710971772 +/- 0.001270585483397847</t>
+          <t>0.004876130554463265 +/- 0.0013644790855601367</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>0.0035391270153362743 +/- 0.002012816970832836</t>
+          <t>0.0012583562721195873 +/- 0.0012285095833121018</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-0.0007864726700746672 +/- 0.001292306466783722</t>
+          <t>-0.0008257963035784299 +/- 0.001930065464696513</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>0.00023594180102245454 +/- 0.0008828133826442612</t>
+          <t>3.3306690738754695e-17 +/- 0.0006811053116668808</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>-0.0006291781360597381 +/- 0.0009823040500823194</t>
+          <t>-0.0004325599685410464 +/- 0.0005406105813947047</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>-0.0051120723554856085 +/- 0.001069718482794758</t>
+          <t>0.0017302398741644409 +/- 0.0004378894504781631</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-0.0005505308690522459 +/- 0.0016886284352012563</t>
+          <t>0.0004718836020448647 +/- 0.002018953622177499</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>0.00570192685804174 +/- 0.0019042548191589832</t>
+          <t>0.0029492725127802212 +/- 0.0012215670127415793</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4731,92 +4731,92 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>0.0010617381046009288 +/- 0.000726157503445519</t>
+          <t>0.0003145890680299135 +/- 0.0005779370214981953</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>0.0060951631930790786 +/- 0.0011829814358231528</t>
+          <t>0.0020841525756980506 +/- 0.0008624346126410283</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>0.011954384585135713 +/- 0.001706845018813253</t>
+          <t>0.014667715296893457 +/- 0.0016688238438004814</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.0013370035391270906 +/- 0.0006856309781424602</t>
+          <t>0.0008257963035784632 +/- 0.000511207235548566</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-0.0009437672040896183 +/- 0.0009823040500823177</t>
+          <t>1.1102230246251566e-17 +/- 0.0008967168109312807</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>0.005348014156508108 +/- 0.0006626936510559422</t>
+          <t>0.006213134093590278 +/- 0.0013824927905030885</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>0.0008651199370822371 +/- 0.0009272376030319787</t>
+          <t>-0.002556036177742782 +/- 0.0012833007370885324</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>0.005505308690523047 +/- 0.0012923064667837321</t>
+          <t>0.013488006291781407 +/- 0.0011933929143133095</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>0.0012190326386158578 +/- 0.0005950745556595175</t>
+          <t>0.0011797090051121283 +/- 0.0004307688222612519</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>-0.002398741643727842 +/- 0.0017713103624939406</t>
+          <t>0.012033031852143172 +/- 0.002119102412160053</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>-0.0020841525756979617 +/- 0.0008801820403302926</t>
+          <t>0.003617774282343744 +/- 0.0013712619562849051</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>0.0028313016122690216 +/- 0.0006990321995529249</t>
+          <t>0.008808493904836835 +/- 0.0014942980731419695</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>0.003893039716869884 +/- 0.0017181323063274233</t>
+          <t>0.020369642154935152 +/- 0.0017391541004715793</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>0.008454581203303235 +/- 0.0010140618921138452</t>
+          <t>0.0036964215493511697 +/- 0.0015451736299165277</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
         <is>
-          <t>0.016830515139598923 +/- 0.0013253873021118981</t>
+          <t>0.01993708218639405 +/- 0.0019977799128400417</t>
         </is>
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>-3.932363350372947e-05 +/- 0.00011797090051118841</t>
+          <t>-7.864726700744784e-05 +/- 0.00023594180102239903</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>0.002988596146283973 +/- 0.0012082022411118493</t>
+          <t>0.004168305151396046 +/- 0.000561653828434353</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>3.932363350378498e-05 +/- 0.0005950745556595226</t>
+          <t>0.00334250884781756 +/- 0.000951111806720256</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4826,52 +4826,52 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>0.00326386158081009 +/- 0.0008624346126410223</t>
+          <t>0.002595359811246589 +/- 0.0007293447499406681</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>0.0026740070782540703 +/- 0.0009759869167118143</t>
+          <t>0.0038930397168698725 +/- 0.00128570843289593</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>0.00011797090051122173 +/- 0.00018020352713159273</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>0.0009830908375934588 +/- 0.00047351925201698843</t>
+          <t>0.0031852143138026423 +/- 0.00140082682898602</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>-0.0014156508061344386 +/- 0.001441628217052545</t>
+          <t>0.005623279591034258 +/- 0.0011538655722470356</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>0.003303185214313842 +/- 0.000950298542948853</t>
+          <t>-0.004758159653951988 +/- 0.001616100872043614</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>0.00263468344475033 +/- 0.0007471490365709494</t>
+          <t>0.0015729453401494675 +/- 0.0010551638116397142</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>-0.0053480141565080295 +/- 0.0007502471108273267</t>
+          <t>0.0004718836020448647 +/- 0.0016757590053214702</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>0.012780180888714165 +/- 0.001044114671439392</t>
+          <t>0.003853716083366143 +/- 0.000927237603032003</t>
         </is>
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>0.0018088871411718777 +/- 0.001452315006891006</t>
+          <t>-0.0009437672040896294 +/- 0.001330045971316389</t>
         </is>
       </c>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-0.000126796280642405 +/- 0.0010532490105137169</t>
+          <t>0.000126796280642405 +/- 0.001376711536340017</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4891,157 +4891,157 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.003465765004226529 +/- 0.0017405968116630643</t>
+          <t>0.0032544378698224573 +/- 0.001626532663135576</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.006255283178360105 +/- 0.0010143702451394648</t>
+          <t>-0.0016060862214708703 +/- 0.0011466322879332624</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.0012679628064243497 +/- 0.001085818476641167</t>
+          <t>-0.0026204564666103326 +/- 0.0013864090842651581</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.004099746407438709 +/- 0.0019918633420030764</t>
+          <t>0.0038884192730346155 +/- 0.0017811756133309564</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.007945900253592564 +/- 0.000996604067840391</t>
+          <t>0.003719357565511383 +/- 0.0010490003081987075</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.000676246830093008 +/- 0.0004706478751335462</t>
+          <t>0.00016906170752321037 +/- 0.0002803571251356886</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.004226542688081159 +/- 0.0015586719285364075</t>
+          <t>0.006508875739644926 +/- 0.0016281792294385725</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.019061707523245975 +/- 0.0017876826697004748</t>
+          <t>0.01322907861369398 +/- 0.003134772889397906</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.01766694843617921 +/- 0.0018596787827557218</t>
+          <t>0.016483516483516446 +/- 0.002563947741014876</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-0.0015638207945900206 +/- 0.0013636742015977804</t>
+          <t>-0.0021132713440406015 +/- 0.0013760626032206093</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.004015215553677098 +/- 0.0006051488192424586</t>
+          <t>-0.001986475063398163 +/- 0.0012256973795435639</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.0010566356720203007 +/- 0.0012992752450498128</t>
+          <t>-0.004606931530008485 +/- 0.0012742868496772165</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.010693153000845312 +/- 0.003065627693286325</t>
+          <t>0.00828402366863903 +/- 0.0024072748716649386</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.009467455621301779 +/- 0.0026677487469246963</t>
+          <t>0.004353338968723563 +/- 0.0017431606616484588</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0.004649196956889257 +/- 0.0013365501522266988</t>
+          <t>0.004691462383770028 +/- 0.0016953652679739248</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>0.0030431107354184305 +/- 0.0014494022146646058</t>
+          <t>-0.0010566356720203118 +/- 0.0013793042157295525</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>0.00012679628064244942 +/- 0.0015244876413247081</t>
+          <t>0.004099746407438665 +/- 0.0019280633521482765</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>0.0032121724429416743 +/- 0.0010213901921889113</t>
+          <t>-0.002535925612848722 +/- 0.0010692401217813699</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.0005494505494505808 +/- 0.0004247622832257397</t>
+          <t>-0.00025359256128489884 +/- 0.0002070574592378247</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.0010143702451394954 +/- 0.0016714894280037992</t>
+          <t>0.004057480980557882 +/- 0.0018345337628242237</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>0.0019019442096365302 +/- 0.0014049678899910958</t>
+          <t>-0.003338968723584157 +/- 0.0018849622249347317</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>0.0013524936601859827 +/- 0.0008410713754070971</t>
+          <t>4.226542688077206e-05 +/- 0.0008336045191596053</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.0005917159763313862 +/- 0.0004310244728311765</t>
+          <t>-0.001479289940828421 +/- 0.0005429092383205835</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.0009721048182586456 +/- 0.0006828188681911901</t>
+          <t>-0.0024091293322062945 +/- 0.0014768727987875213</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.0009721048182586789 +/- 0.0006561358705096971</t>
+          <t>-0.00046491969568895897 +/- 0.0006395919674734345</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>0.002451394759087078 +/- 0.001333874373462326</t>
+          <t>-0.007100591715976356 +/- 0.0015678137777676683</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>-0.0028317836010143594 +/- 0.0024209642420320856</t>
+          <t>0.017540152155536736 +/- 0.0014176255140530944</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>0.000295857988165682 +/- 0.0018716474915878671</t>
+          <t>0.008368554522400673 +/- 0.002210768694948788</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.00976331360946745 +/- 0.0033196526569499447</t>
+          <t>0.01424344885883344 +/- 0.0027975115373411303</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>4.226542688083868e-05 +/- 0.00039873123973187936</t>
+          <t>0.0007607776838545743 +/- 0.0002535925612848766</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.00016906170752323257 +/- 0.0004706478751335482</t>
+          <t>-0.00038038884192732604 +/- 0.0006110241882840578</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -5051,122 +5051,122 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.008579881656804733 +/- 0.0020536822676680095</t>
+          <t>0.00595942519019439 +/- 0.001684795556043506</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.0015638207945900206 +/- 0.0017431606616484681</t>
+          <t>0.006043956043956011 +/- 0.0018524604396289975</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>0.0008030431107354131 +/- 0.0001267962806424161</t>
+          <t>-0.0008875739644970571 +/- 0.00039873123973187936</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>0.00021132713440407124 +/- 0.0007619508189906874</t>
+          <t>0.0013524936601859272 +/- 0.0003162854933874861</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-4.2265426880805365e-05 +/- 0.0009721048182586683</t>
+          <t>-0.0028317836010144037 +/- 0.0010866407550450185</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>0.0015215553677092263 +/- 0.0012566414832898129</t>
+          <t>0.005367709213863014 +/- 0.000983068753137189</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-0.0016060862214708372 +/- 0.00045521257879413364</t>
+          <t>-0.0013524936601859937 +/- 0.0011150385425420962</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.0007185122569738134 +/- 0.0005992158444107139</t>
+          <t>-0.0034234995773457675 +/- 0.0009903106097937427</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.0007607776838546188 +/- 0.002034016807356866</t>
+          <t>0.008833474218089587 +/- 0.0021588491613055093</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.00021132713440408235 +/- 0.001122224687011985</t>
+          <t>0.0005917159763313307 +/- 0.0009298393913778391</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.0037616229923922327 +/- 0.0010600115134390838</t>
+          <t>-0.005198647506339848 +/- 0.0016265326631355781</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>-0.001183431952662717 +/- 0.0011309457447387762</t>
+          <t>-0.005325443786982275 +/- 0.0015144947478587356</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-0.00021132713440403795 +/- 0.0008713240967070345</t>
+          <t>-0.0017328825021132865 +/- 0.0007185122569737997</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>0.004733727810650889 +/- 0.0012365797834596778</t>
+          <t>-4.226542688083868e-05 +/- 0.0012169213904385508</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-0.00016906170752322146 +/- 0.00020705745923777034</t>
+          <t>-0.00025359256128488773 +/- 0.0004706478751335621</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>-0.0008453085376162184 +/- 0.0009259891082082394</t>
+          <t>-0.006297548605240955 +/- 0.00044126401136562537</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.0004226542688081314 +/- 0.0017528690915746092</t>
+          <t>-0.011665257819104002 +/- 0.0015026533249899536</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>0.0010566356720203007 +/- 0.0011991767505588468</t>
+          <t>-0.00046491969568894785 +/- 0.0010430230498100494</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.002789518174133554 +/- 0.0011053843474744</t>
+          <t>-0.003550295857988195 +/- 0.00128475774755458</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>0.0001267962806424605 +/- 0.0003803888419272952</t>
+          <t>8.453085376159963e-05 +/- 0.0005917159763313482</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.00038038884192733715 +/- 0.0005810535538827987</t>
+          <t>-0.00046491969568894785 +/- 0.0005494505494505312</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>-0.0005917159763313418 +/- 0.0005071851225697624</t>
+          <t>-0.003127641589180086 +/- 0.0008282298369512196</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>0.004395604395604413 +/- 0.001003748274474884</t>
+          <t>-0.007396449704142038 +/- 0.001454937825702348</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>0.0002535925612848766 +/- 0.001121428500542839</t>
+          <t>-0.007945900253592587 +/- 0.0013338743734623458</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5176,92 +5176,92 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>0.0008030431107354352 +/- 0.0005494505494505484</t>
+          <t>-0.0005494505494505697 +/- 0.0003803888419272767</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>-0.0010566356720202786 +/- 0.0009497973395707554</t>
+          <t>0.0015638207945899985 +/- 0.0008875739644970576</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>0.0021555367709213957 +/- 0.0013020221302408365</t>
+          <t>-0.008791208791208815 +/- 0.0011150385425420979</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>-0.001563820794590043 +/- 0.0003301035365979035</t>
+          <t>-0.00046491969568893674 +/- 0.000441264011365601</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-0.00021132713440403795 +/- 0.001004637728149193</t>
+          <t>0.001437024513947549 +/- 0.0013524936601859766</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-0.0031276415891800524 +/- 0.0015144947478587226</t>
+          <t>-0.009213863060016935 +/- 0.0008825280227312465</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>0.0013947590870667993 +/- 0.0011811655631852934</t>
+          <t>0.0001267962806423939 +/- 0.0013372182603175237</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-0.0020287404902789574 +/- 0.0015215553677092196</t>
+          <t>-0.006593406593406637 +/- 0.002072299352853971</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>4.226542688083868e-05 +/- 0.0002958579881656804</t>
+          <t>-0.00021132713440408235 +/- 0.0003407547653549671</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>-0.005705832628909546 +/- 0.0011690039464023175</t>
+          <t>-0.0023245984784446504 +/- 0.0017452090297601472</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.0015638207945900206 +/- 0.0020185890002129376</t>
+          <t>-0.0025781910397295383 +/- 0.0012459343172429229</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>-0.0043956043956044025 +/- 0.001168239641680944</t>
+          <t>-0.0008030431107354352 +/- 0.0010257532628496731</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>-0.007480980557903627 +/- 0.0017016755823497421</t>
+          <t>-0.006382079459002554 +/- 0.0024017028985926442</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>0.0013947590870667993 +/- 0.002096723035471258</t>
+          <t>-0.0043956043956044355 +/- 0.0008495245664514607</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
         <is>
-          <t>-0.005367709213863048 +/- 0.001763537281912523</t>
+          <t>0.0019019442096364636 +/- 0.0013921951895182391</t>
         </is>
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>0.00021132713440408235 +/- 0.00021132713440408232</t>
+          <t>-0.0006762468300929969 +/- 0.00043102447283117657</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>-0.0009721048182586677 +/- 0.0005362881462573955</t>
+          <t>0.0005494505494505142 +/- 0.0009269531783373092</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>-0.00038038884192728164 +/- 0.0004800429709045148</t>
+          <t>-0.00287404902789522 +/- 0.0005278950125442396</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>0.0007185122569738245 +/- 0.0006828188681911826</t>
+          <t>-0.0021978021978022234 +/- 0.0009785153763981747</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>0.0007185122569737911 +/- 0.0015477458515300543</t>
+          <t>-0.00021132713440407124 +/- 0.0017554150175228224</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5286,37 +5286,37 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>-0.0004226542688080981 +/- 0.0006268975897798596</t>
+          <t>-0.0006762468300930191 +/- 0.0004310244728311743</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>0.0008453085376162517 +/- 0.0011182380858260925</t>
+          <t>0.003719357565511372 +/- 0.0013992346033175715</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>-0.00029585798816565977 +/- 0.0011029575951563813</t>
+          <t>-0.007438715131022844 +/- 0.0019842256287921625</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>-0.0021555367709213845 +/- 0.0009535514938865955</t>
+          <t>-0.0008453085376162517 +/- 0.0004226542688080981</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>-0.00025359256128484333 +/- 0.0015262443013751253</t>
+          <t>-0.006677937447168247 +/- 0.0017199484318999006</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>-0.003127641589180041 +/- 0.0021401502791499796</t>
+          <t>0.0002535925612848322 +/- 0.002647584068193709</t>
         </is>
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>0.0005494505494505586 +/- 0.0010187633806588178</t>
+          <t>-0.00033812341504652066 +/- 0.0014616751027718077</t>
         </is>
       </c>
     </row>
